--- a/CortexKitchen_Progress_Tracker_v4.xlsx
+++ b/CortexKitchen_Progress_Tracker_v4.xlsx
@@ -1042,7 +1042,7 @@
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="77" t="inlineStr">
         <is>
-          <t>Last completed: P6-00c — drop Diff 1, v3 reseed, stale_assumptions fix (2026-06-26)</t>
+          <t>Last completed: P6-S02 — connectors table + async job queue (2026-06-27)</t>
         </is>
       </c>
       <c r="B4" s="44" t="inlineStr">
@@ -1078,7 +1078,7 @@
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="76" t="inlineStr">
         <is>
-          <t>Stable: main + dev in sync (P6-00a/b/c merged to main 2026-06-27); next: P6-S01</t>
+          <t>Stable: main + dev in sync (P6-S01/S02 merged to dev 2026-06-27); next: P6-S03 (swiggy-sync-orders)</t>
         </is>
       </c>
       <c r="B5" s="49" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="H9" s="44" t="inlineStr">
         <is>
-          <t>docs/CONNECTORS.md (new), docs/ARCHITECTURE.md, CLAUDE.md, docs/DECISIONS.md (D-019)</t>
+          <t>docs/ARCHITECTURE.md (connector layer section), docs/DECISIONS.md (D-019), docs/DATA_MODEL.md, CLAUDE.md (new), docs/SWIGGY_INTEGRATION.md</t>
         </is>
       </c>
       <c r="I9" s="45" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J9" s="46" t="inlineStr">
@@ -13339,14 +13339,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L9" s="43" t="inlineStr"/>
+      <c r="L9" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
       <c r="M9" s="43" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N9" s="47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="44" t="inlineStr">
         <is>
@@ -13355,7 +13359,7 @@
       </c>
       <c r="P9" s="44" t="inlineStr">
         <is>
-          <t>is_available() True/False; call_tool() 401 re-auth + 5xx retry; get_addresses returns data end-to-end</t>
+          <t>13/13 pass — test_swiggy_client.py (7): is_available, 401 no-retry, 500 retry x2, success data, never raises, success=false; test_connector_repository.py (6): upsert create, upsert idempotent, get none, error_count increment, error clear on success, list_active filter</t>
         </is>
       </c>
     </row>
@@ -13397,12 +13401,12 @@
       </c>
       <c r="H10" s="49" t="inlineStr">
         <is>
-          <t>docs/DATA_MODEL.md (connectors table), docs/DATA_SOURCES.md (new), docs/APIS.md (job status endpoint)</t>
+          <t>docs/DATA_MODEL.md (connectors table, orders/reservations/feedback new cols), docs/ARCHITECTURE.md, docs/DECISIONS.md (D-019)</t>
         </is>
       </c>
       <c r="I10" s="45" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J10" s="46" t="inlineStr">
@@ -13415,14 +13419,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L10" s="48" t="inlineStr"/>
+      <c r="L10" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
       <c r="M10" s="48" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N10" s="50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="49" t="inlineStr">
         <is>
@@ -13431,7 +13439,7 @@
       </c>
       <c r="P10" s="49" t="inlineStr">
         <is>
-          <t>Migration smoke test; token encryption round-trip; async run returns job_id immediately; status endpoint polls correctly</t>
+          <t>Migration smoke test (alembic upgrade head verified live on DB); connectors table + all new cols confirmed via psycopg2; swiggy_delivery enum value present</t>
         </is>
       </c>
     </row>
@@ -16178,7 +16186,7 @@
       </c>
       <c r="D4" s="72" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Updated (status + signatures)</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16274,7 @@
       </c>
       <c r="D8" s="73" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Updated (P6-S01/S02 done)</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16340,7 @@
       </c>
       <c r="D11" s="73" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Updated (P6-S02 done)</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16362,7 @@
       </c>
       <c r="D12" s="73" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Updated (D-019 added P6-S01)</t>
         </is>
       </c>
     </row>
@@ -16442,7 +16450,7 @@
       </c>
       <c r="D16" s="73" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Created (P6-S01 done)</t>
         </is>
       </c>
     </row>

--- a/CortexKitchen_Progress_Tracker_v4.xlsx
+++ b/CortexKitchen_Progress_Tracker_v4.xlsx
@@ -7989,7 +7989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8014,7 +8014,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="31" t="inlineStr">
         <is>
-          <t>CortexKitchen — Phase Tracker (P0 through P6-00c complete)</t>
+          <t>CortexKitchen — Phase Tracker (P0 through P6-S02 complete)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,172 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="8" customHeight="1"/>
+    <row r="72" ht="8" customHeight="1">
+      <c r="A72" s="87" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B72" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="88" t="inlineStr">
+        <is>
+          <t>P6-S01</t>
+        </is>
+      </c>
+      <c r="D72" s="88" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="E72" s="88" t="inlineStr">
+        <is>
+          <t>BaseConnector + SwiggyMCPClient</t>
+        </is>
+      </c>
+      <c r="F72" s="88" t="inlineStr">
+        <is>
+          <t>BaseConnector ABC (sync/enrich), SwiggyMCPClient (JSON-RPC 2.0, httpx, graceful degradation — never raises), SwiggyConnector skeleton, enrichers/ + executor/ package stubs, CLAUDE.md at root, swiggy_access_token + swiggy_address_id in settings</t>
+        </is>
+      </c>
+      <c r="G72" s="88" t="inlineStr">
+        <is>
+          <t>feature/swiggy-base-connector</t>
+        </is>
+      </c>
+      <c r="H72" s="84" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I72" s="51" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J72" s="87" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K72" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="L72" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="M72" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="N72" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" s="88" t="inlineStr">
+        <is>
+          <t>P6-00c</t>
+        </is>
+      </c>
+      <c r="P72" s="88" t="inlineStr">
+        <is>
+          <t>7 tests: is_available True/False; call_tool returns None on 401, 500 (x2 retry verified), success data dict, never raises on Exception, returns None on success=false</t>
+        </is>
+      </c>
+      <c r="Q72" s="88" t="inlineStr">
+        <is>
+          <t>Merged to dev 2026-06-27. PR #80. CLAUDE.md created. Migration verified live on DB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="87" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B73" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="88" t="inlineStr">
+        <is>
+          <t>P6-S02</t>
+        </is>
+      </c>
+      <c r="D73" s="88" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="E73" s="88" t="inlineStr">
+        <is>
+          <t>connectors table + async job queue</t>
+        </is>
+      </c>
+      <c r="F73" s="88" t="inlineStr">
+        <is>
+          <t>Alembic migration b3e1f2a9c5d7: connectors table (11 cols, uq org+type), orders.source/channel/external_order_id, reservations.source/external_booking_id, feedback delivery timing cols, swiggy_delivery enum value. ConnectorRepository (upsert, token, sync status). Redis async job queue (24h TTL, uuid4 IDs, no external library).</t>
+        </is>
+      </c>
+      <c r="G73" s="88" t="inlineStr">
+        <is>
+          <t>feature/swiggy-base-connector</t>
+        </is>
+      </c>
+      <c r="H73" s="84" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I73" s="51" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J73" s="87" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K73" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="L73" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="M73" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="N73" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" s="88" t="inlineStr">
+        <is>
+          <t>P6-S01</t>
+        </is>
+      </c>
+      <c r="P73" s="88" t="inlineStr">
+        <is>
+          <t>6 tests: upsert creates, upsert idempotent (1 row), get returns None, error_count increments, error clears on success, list_active filter. Migration smoke: alembic upgrade head + psycopg2 verify all cols + enum.</t>
+        </is>
+      </c>
+      <c r="Q73" s="88" t="inlineStr">
+        <is>
+          <t>Merged to dev 2026-06-27. PR #80. Migration verified live on Docker Postgres.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A40:Q40"/>
@@ -16619,7 +16784,7 @@
       </c>
       <c r="D4" s="44" t="inlineStr">
         <is>
-          <t>Phase 3 already synced</t>
+          <t>Phase 6 on dev (P6-S01/S02 merged). main has P5 + P6-00 series. Next main sync: end of Phase 6.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -16663,7 +16828,7 @@
       </c>
       <c r="D5" s="49" t="inlineStr">
         <is>
-          <t>Current working base</t>
+          <t>Current working base — Phase 6 active (P6-S01/S02 complete, P6-S03 next)</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>

--- a/CortexKitchen_Progress_Tracker_v4.xlsx
+++ b/CortexKitchen_Progress_Tracker_v4.xlsx
@@ -1042,7 +1042,7 @@
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="77" t="inlineStr">
         <is>
-          <t>Last completed: P6-S02 — connectors table + async job queue (2026-06-27)</t>
+          <t>Last completed: P6-S03 — SwiggyOrderSyncService, get_food_orders → orders table (2026-06-27)</t>
         </is>
       </c>
       <c r="B4" s="44" t="inlineStr">
@@ -1078,7 +1078,7 @@
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="76" t="inlineStr">
         <is>
-          <t>Stable: main + dev in sync (P6-S01/S02 merged to dev 2026-06-27); next: P6-S03 (swiggy-sync-orders)</t>
+          <t>Stable: main + dev in sync through P6-S03; next: P6-S04 (swiggy-sync-reservations)</t>
         </is>
       </c>
       <c r="B5" s="49" t="inlineStr">
@@ -7989,7 +7989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13027,6 +13027,89 @@
       <c r="Q73" s="88" t="inlineStr">
         <is>
           <t>Merged to dev 2026-06-27. PR #80. Migration verified live on Docker Postgres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="87" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B74" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" s="88" t="inlineStr">
+        <is>
+          <t>P6-S03</t>
+        </is>
+      </c>
+      <c r="D74" s="88" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="E74" s="88" t="inlineStr">
+        <is>
+          <t>SwiggyOrderSyncService — get_food_orders → orders table</t>
+        </is>
+      </c>
+      <c r="F74" s="88" t="inlineStr">
+        <is>
+          <t>SwiggyOrderSyncService.sync(address_id): fetches up to 20 Swiggy delivery orders, creates one Order row per item (source=swiggy, channel=delivery, is_delivery=True, external_order_id={orderId}_{idx}). _get_or_create_menu_item: case-insensitive name match; placeholder (is_available=False) if no match. Idempotent. SwiggyConnector.sync() implemented: reads SWIGGY_ADDRESS_ID, sets connector status syncing→success/error. BaseConnector updated: db: Session added to __init__.</t>
+        </is>
+      </c>
+      <c r="G74" s="88" t="inlineStr">
+        <is>
+          <t>feature/swiggy-sync-orders</t>
+        </is>
+      </c>
+      <c r="H74" s="84" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I74" s="51" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J74" s="87" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K74" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="L74" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="M74" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="N74" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" s="88" t="inlineStr">
+        <is>
+          <t>P6-S02</t>
+        </is>
+      </c>
+      <c r="P74" s="88" t="inlineStr">
+        <is>
+          <t>8/8 pass: correct count, Order fields, placeholder MenuItem, reuse existing MenuItem, idempotency, None graceful, empty list, ext_id format</t>
+        </is>
+      </c>
+      <c r="Q74" s="88" t="inlineStr">
+        <is>
+          <t>Merged to dev 2026-06-27. Mock-first (no Swiggy token needed). Live integration test pending token.</t>
         </is>
       </c>
     </row>
@@ -13669,12 +13752,12 @@
       </c>
       <c r="H13" s="44" t="inlineStr">
         <is>
-          <t>docs/DATA_SOURCES.md (Swiggy orders), docs/DATA_MODEL.md (source+channel cols), docs/AGENTS.md (demand_forecast updated)</t>
+          <t>docs/SWIGGY_INTEGRATION.md (P6-S03 ✅, status header updated)</t>
         </is>
       </c>
       <c r="I13" s="45" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J13" s="51" t="inlineStr">
@@ -13687,14 +13770,18 @@
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L13" s="43" t="inlineStr"/>
+      <c r="L13" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
       <c r="M13" s="43" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N13" s="47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="44" t="inlineStr">
         <is>
@@ -13703,7 +13790,7 @@
       </c>
       <c r="P13" s="44" t="inlineStr">
         <is>
-          <t>Sync idempotency (run twice = no duplicates); ForecastService channel filter test; orders table has source=swiggy rows after sync</t>
+          <t>8/8 pass — correct count, correct Order fields (source/channel/is_delivery), placeholder MenuItem creation (is_available=False, category=swiggy_import), reuse existing MenuItem by name, idempotency on duplicate sync, None call_tool graceful, empty order list, external_order_id format SW-001_0/SW-001_1</t>
         </is>
       </c>
     </row>
@@ -16346,12 +16433,12 @@
       </c>
       <c r="C4" s="49" t="inlineStr">
         <is>
-          <t>P6-D01 — NEW</t>
+          <t>P6-D01 — updated P6-S01/S02/S03</t>
         </is>
       </c>
       <c r="D4" s="72" t="inlineStr">
         <is>
-          <t>Updated (status + signatures)</t>
+          <t>Updated (P6-S03 status ✅)</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16915,7 @@
       </c>
       <c r="D5" s="49" t="inlineStr">
         <is>
-          <t>Current working base — Phase 6 active (P6-S01/S02 complete, P6-S03 next)</t>
+          <t>Current working base — Phase 6 active (P6-S01/S02/S03 complete, P6-S04 next)</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>

--- a/CortexKitchen_Progress_Tracker_v4.xlsx
+++ b/CortexKitchen_Progress_Tracker_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Tracker" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 6" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doc Strategy" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git Practices" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Phase Tracker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Phase 6" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Doc Strategy" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Git Practices" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1078,7 +1078,7 @@
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="76" t="inlineStr">
         <is>
-          <t>Stable: main + dev in sync through P6-S03; next: P6-S04 (swiggy-sync-reservations)</t>
+          <t>Stable: dev through P6-S03; P6-S04 (agent-intelligence) IN PROGRESS → next: P6-S05 (Dineout sync, token pending)</t>
         </is>
       </c>
       <c r="B5" s="49" t="inlineStr">
@@ -7989,7 +7989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13113,6 +13113,85 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="87" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B75" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" s="88" t="inlineStr">
+        <is>
+          <t>P6-S04</t>
+        </is>
+      </c>
+      <c r="D75" s="88" t="inlineStr">
+        <is>
+          <t>Agents + Infra</t>
+        </is>
+      </c>
+      <c r="E75" s="88" t="inlineStr">
+        <is>
+          <t>Agent Intelligence Bundle</t>
+        </is>
+      </c>
+      <c r="F75" s="88" t="inlineStr">
+        <is>
+          <t>Aggregator contradiction detection (0 LLM calls). Critic replanning loop max 2 retries. Qdrant early enrichment layer. Semantic cache (planning + chatbot, Qdrant, threshold 0.92). Chatbot tool use via Groq function calling. Cross-session memory in Qdrant. Proactive pattern surfacing on session start.</t>
+        </is>
+      </c>
+      <c r="G75" s="88" t="inlineStr">
+        <is>
+          <t>feature/agent-intelligence</t>
+        </is>
+      </c>
+      <c r="H75" s="84" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I75" s="51" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="J75" s="87" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="K75" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="L75" s="87" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="M75" s="87" t="inlineStr"/>
+      <c r="N75" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="88" t="inlineStr">
+        <is>
+          <t>P6-S03</t>
+        </is>
+      </c>
+      <c r="P75" s="88" t="inlineStr">
+        <is>
+          <t>Contradiction fires; replanning routes correctly; cache hit; chatbot tools return data; cross-session memory persists</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Building now (2026-06-27). Mock-first where needed. No Swiggy token required.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A40:Q40"/>
@@ -13136,7 +13215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P60"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -13795,2546 +13874,2625 @@
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="B14" s="48" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
         <is>
           <t>P6-S04</t>
         </is>
       </c>
-      <c r="C14" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-sync-reservations</t>
-        </is>
-      </c>
-      <c r="D14" s="49" t="inlineStr">
+      <c r="C14" s="44" t="inlineStr">
+        <is>
+          <t>feature/agent-intelligence</t>
+        </is>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>Agents + Infra</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>Agent Intelligence Bundle — smarter pipeline + agentic chatbot</t>
+        </is>
+      </c>
+      <c r="F14" s="44" t="inlineStr">
+        <is>
+          <t>Aggregator contradiction detection (pure Python, 0 LLM calls): detects demand_forecast vs inventory conflicts, appends DETECTED CONTRADICTIONS to critic summary. Critic replanning loop: rejected/revision → replan_orchestrator injects critic notes → aggregator re-runs → critic re-evaluates, max 2 retries (+1 LLM call/retry). Qdrant early enrichment: 1 shared retrieval step before parallel nodes, all agents get pre-loaded context. Semantic cache: Qdrant embedding-based lookup (threshold 0.92) for planning runs + chatbot queries. Chatbot tool use: Groq function calling — query_runs, get_run_detail, trigger_planning_run, get_inventory_status. Cross-session memory: Qdrant session summaries per user. Proactive pattern surfacing: chatbot detects recurring critic failures on session start.</t>
+        </is>
+      </c>
+      <c r="G14" s="44" t="inlineStr">
+        <is>
+          <t>feat: agent intelligence — contradiction detection, replanning loop, semantic cache, agentic chatbot</t>
+        </is>
+      </c>
+      <c r="H14" s="44" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md (replanning loop, Qdrant enrichment), docs/AGENTS.md (aggregator update)</t>
+        </is>
+      </c>
+      <c r="I14" s="45" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J14" s="51" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K14" s="43" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L14" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="M14" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N14" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="44" t="inlineStr">
+        <is>
+          <t>P6-S03</t>
+        </is>
+      </c>
+      <c r="P14" s="44" t="inlineStr">
+        <is>
+          <t>Contradiction detection: demand_forecast vs inventory conflict fires correctly. Replanning: rejected plan routes back, critic re-evaluates with notes. Semantic cache: cache hit returns plan without LLM call. Chatbot tools: query_runs returns structured data; trigger_planning_run starts a run. Cross-session memory: session summary persists in Qdrant, retrieved on next session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B15" s="48" t="inlineStr">
+        <is>
+          <t>P6-S05</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>Waiting: Swiggy token pending</t>
+        </is>
+      </c>
+      <c r="D15" s="49" t="inlineStr">
         <is>
           <t>Integrations</t>
         </is>
       </c>
-      <c r="E14" s="49" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>Sync Dineout bookings → reservations table</t>
         </is>
       </c>
-      <c r="F14" s="49" t="inlineStr">
+      <c r="F15" s="49" t="inlineStr">
         <is>
           <t>get_booking_status for all active Dineout bookings → reservations table with source='dineout'. Track confirmed/no-show/cancelled. ReservationService gains source filter. Absorbs original P6-04 for Dineout channel (Resy/OpenTable deferred to P6-R02).</t>
         </is>
       </c>
-      <c r="G14" s="49" t="inlineStr">
+      <c r="G15" s="49" t="inlineStr">
         <is>
           <t>feat: dineout reservation sync — get_booking_status → reservations table (source=dineout)</t>
         </is>
       </c>
-      <c r="H14" s="49" t="inlineStr">
+      <c r="H15" s="49" t="inlineStr">
         <is>
           <t>docs/DATA_SOURCES.md (Dineout reservations), docs/DATA_MODEL.md</t>
         </is>
       </c>
-      <c r="I14" s="45" t="inlineStr">
+      <c r="I15" s="45" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="J15" s="51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K15" s="48" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L15" s="48" t="inlineStr"/>
+      <c r="M15" s="48" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="N15" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="49" t="inlineStr">
+        <is>
+          <t>P6-S02</t>
+        </is>
+      </c>
+      <c r="P15" s="49" t="inlineStr">
+        <is>
+          <t>Sync idempotency; source filter on ReservationService; booking status mapping test</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="6" customHeight="1">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>P6-S06</t>
+        </is>
+      </c>
+      <c r="C16" s="44" t="inlineStr">
+        <is>
+          <t>Waiting: Swiggy token pending</t>
+        </is>
+      </c>
+      <c r="D16" s="44" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="inlineStr">
+        <is>
+          <t>Sync delivery performance → feedback table</t>
+        </is>
+      </c>
+      <c r="F16" s="44" t="inlineStr">
+        <is>
+          <t>track_food_order → feedback rows: source='swiggy_delivery', prep_time_actual, delivery_time_actual, promised_time, late_flag. ComplaintService surfaces delivery latency patterns. RAG runs over real delivery feedback in Qdrant.</t>
+        </is>
+      </c>
+      <c r="G16" s="44" t="inlineStr">
+        <is>
+          <t>feat: swiggy delivery signal sync — track_food_order → feedback table (source=swiggy_delivery)</t>
+        </is>
+      </c>
+      <c r="H16" s="44" t="inlineStr">
+        <is>
+          <t>docs/DATA_SOURCES.md (delivery feedback), docs/AGENTS.md (complaint_intel updated)</t>
+        </is>
+      </c>
+      <c r="I16" s="45" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="J16" s="51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K16" s="43" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L16" s="43" t="inlineStr"/>
+      <c r="M16" s="43" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="N16" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="44" t="inlineStr">
+        <is>
+          <t>P6-S03</t>
+        </is>
+      </c>
+      <c r="P16" s="44" t="inlineStr">
+        <is>
+          <t>Latency mapping test; late_flag logic; ComplaintService source filter; RAG retrieval returns real delivery complaints</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1"/>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="52" t="inlineStr">
+        <is>
+          <t>WEEK 3 — Market Intelligence: Live Enrichment</t>
+        </is>
+      </c>
+      <c r="B18" s="103" t="n"/>
+      <c r="C18" s="103" t="n"/>
+      <c r="D18" s="103" t="n"/>
+      <c r="E18" s="103" t="n"/>
+      <c r="F18" s="103" t="n"/>
+      <c r="G18" s="103" t="n"/>
+      <c r="H18" s="103" t="n"/>
+      <c r="I18" s="103" t="n"/>
+      <c r="J18" s="103" t="n"/>
+      <c r="K18" s="103" t="n"/>
+      <c r="L18" s="103" t="n"/>
+      <c r="M18" s="103" t="n"/>
+      <c r="N18" s="103" t="n"/>
+      <c r="O18" s="103" t="n"/>
+      <c r="P18" s="104" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="53" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B19" s="53" t="inlineStr">
+        <is>
+          <t>P6-S07</t>
+        </is>
+      </c>
+      <c r="C19" s="54" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-enrichers</t>
+        </is>
+      </c>
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="E19" s="54" t="inlineStr">
+        <is>
+          <t>CompetitorEnricher — Food MCP</t>
+        </is>
+      </c>
+      <c r="F19" s="54" t="inlineStr">
+        <is>
+          <t>search_restaurants (cuisine, addressId) → filter OPEN → search_menu + get_restaurant_menu per restaurant (max 3) → competitor_pricing dict: area avg price per dish category, pricing alerts vs your menu. Redis cache 30min TTL. Supersedes original P6-07 (no scraping needed).</t>
+        </is>
+      </c>
+      <c r="G19" s="54" t="inlineStr">
+        <is>
+          <t>feat: CompetitorEnricher — live competitor pricing via Food MCP</t>
+        </is>
+      </c>
+      <c r="H19" s="54" t="inlineStr">
+        <is>
+          <t>docs/SWIGGY_INTEGRATION.md (new, CompetitorEnricher section), docs/AGENTS.md (menu_intel updated)</t>
+        </is>
+      </c>
+      <c r="I19" s="45" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J14" s="51" t="inlineStr">
+      <c r="J19" s="51" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K14" s="48" t="inlineStr">
+      <c r="K19" s="53" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L14" s="48" t="inlineStr"/>
-      <c r="M14" s="48" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="N14" s="50" t="n">
+      <c r="L19" s="53" t="inlineStr"/>
+      <c r="M19" s="53" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="N19" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="49" t="inlineStr">
+      <c r="O19" s="54" t="inlineStr">
         <is>
           <t>P6-S02</t>
         </is>
       </c>
-      <c r="P14" s="49" t="inlineStr">
-        <is>
-          <t>Sync idempotency; source filter on ReservationService; booking status mapping test</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="B15" s="43" t="inlineStr">
-        <is>
-          <t>P6-S05</t>
-        </is>
-      </c>
-      <c r="C15" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-sync-feedback</t>
-        </is>
-      </c>
-      <c r="D15" s="44" t="inlineStr">
+      <c r="P19" s="54" t="inlineStr">
+        <is>
+          <t>Structured dict with area_avg_price; graceful None on failure; Redis cache hit; menu_intel prompt includes market context</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>P6-S08</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-enrichers</t>
+        </is>
+      </c>
+      <c r="D20" s="49" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t>OccupancyEnricher — Dineout MCP</t>
+        </is>
+      </c>
+      <c r="F20" s="49" t="inlineStr">
+        <is>
+          <t>get_saved_locations → search_restaurants_dineout → get_restaurant_details (top 3) → get_available_slots (today) → occupancy_signal: HIGH/MEDIUM/LOW, tonight_busy bool. Redis cache 30min TTL. Supersedes original P6-06 Google Trends approach.</t>
+        </is>
+      </c>
+      <c r="G20" s="49" t="inlineStr">
+        <is>
+          <t>feat: OccupancyEnricher — live competitor occupancy via Dineout MCP</t>
+        </is>
+      </c>
+      <c r="H20" s="49" t="inlineStr">
+        <is>
+          <t>docs/SWIGGY_INTEGRATION.md (OccupancyEnricher section), docs/AGENTS.md (reservation updated)</t>
+        </is>
+      </c>
+      <c r="I20" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J20" s="51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K20" s="48" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L20" s="48" t="inlineStr"/>
+      <c r="M20" s="48" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="N20" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="49" t="inlineStr">
+        <is>
+          <t>P6-S07</t>
+        </is>
+      </c>
+      <c r="P20" s="49" t="inlineStr">
+        <is>
+          <t>HIGH/MEDIUM/LOW logic test; graceful None; reservation node prompt includes occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B21" s="53" t="inlineStr">
+        <is>
+          <t>P6-S09</t>
+        </is>
+      </c>
+      <c r="C21" s="54" t="inlineStr">
+        <is>
+          <t>feature/swiggy-procurement-l1</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="E21" s="54" t="inlineStr">
+        <is>
+          <t>ProcurementEnricher — Instamart (read-only)</t>
+        </is>
+      </c>
+      <c r="F21" s="54" t="inlineStr">
+        <is>
+          <t>For each shortage_alert item: search_products (addressId, ingredient) → spinId, price, unit, availability. Also your_go_to_items for frequent reorder suggestions. procurement_options dict injected into inventory node prompt. spinId stored for later execution.</t>
+        </is>
+      </c>
+      <c r="G21" s="54" t="inlineStr">
+        <is>
+          <t>feat: ProcurementEnricher — live Instamart ingredient pricing injected into inventory node</t>
+        </is>
+      </c>
+      <c r="H21" s="54" t="inlineStr">
+        <is>
+          <t>docs/SWIGGY_INTEGRATION.md (ProcurementEnricher section), docs/AGENTS.md (inventory updated)</t>
+        </is>
+      </c>
+      <c r="I21" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J21" s="51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K21" s="53" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L21" s="53" t="inlineStr"/>
+      <c r="M21" s="53" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="N21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="54" t="inlineStr">
+        <is>
+          <t>P6-S07</t>
+        </is>
+      </c>
+      <c r="P21" s="54" t="inlineStr">
+        <is>
+          <t>procurement_options per shortage item; spinId captured; graceful None; inventory prompt includes live prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="6" customHeight="1">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>P6-S10</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-enrichers</t>
+        </is>
+      </c>
+      <c r="D22" s="49" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="E22" s="49" t="inlineStr">
+        <is>
+          <t>MarketIntelService + 6 new OrchestratorState fields</t>
+        </is>
+      </c>
+      <c r="F22" s="49" t="inlineStr">
+        <is>
+          <t>MarketIntelService orchestrates all 3 enrichers. Adds 6 Annotated[Optional[Dict], keep_last] fields to OrchestratorState: swiggy_competitor_context, swiggy_occupancy_context, swiggy_procurement_options, swiggy_delivery_signal, market_intel_output, dineout_manager_output.</t>
+        </is>
+      </c>
+      <c r="G22" s="49" t="inlineStr">
+        <is>
+          <t>feat: MarketIntelService + 6 new OrchestratorState enrichment fields</t>
+        </is>
+      </c>
+      <c r="H22" s="49" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md (MarketIntelService), docs/DATA_MODEL.md (state fields)</t>
+        </is>
+      </c>
+      <c r="I22" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J22" s="51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K22" s="48" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L22" s="48" t="inlineStr"/>
+      <c r="M22" s="48" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="N22" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="49" t="inlineStr">
+        <is>
+          <t>P6-S07</t>
+        </is>
+      </c>
+      <c r="P22" s="49" t="inlineStr">
+        <is>
+          <t>State field type tests; MarketIntelService runs all 3 enrichers; final_assembler passes through</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1"/>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="52" t="inlineStr">
+        <is>
+          <t>WEEK 4 — New Nodes: Pipeline Expands to 11 Nodes</t>
+        </is>
+      </c>
+      <c r="B24" s="103" t="n"/>
+      <c r="C24" s="103" t="n"/>
+      <c r="D24" s="103" t="n"/>
+      <c r="E24" s="103" t="n"/>
+      <c r="F24" s="103" t="n"/>
+      <c r="G24" s="103" t="n"/>
+      <c r="H24" s="103" t="n"/>
+      <c r="I24" s="103" t="n"/>
+      <c r="J24" s="103" t="n"/>
+      <c r="K24" s="103" t="n"/>
+      <c r="L24" s="103" t="n"/>
+      <c r="M24" s="103" t="n"/>
+      <c r="N24" s="103" t="n"/>
+      <c r="O24" s="103" t="n"/>
+      <c r="P24" s="104" t="n"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="53" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B25" s="53" t="inlineStr">
+        <is>
+          <t>P6-S11</t>
+        </is>
+      </c>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-node</t>
+        </is>
+      </c>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="E25" s="54" t="inlineStr">
+        <is>
+          <t>market_intel_node — 10th LangGraph node</t>
+        </is>
+      </c>
+      <c r="F25" s="54" t="inlineStr">
+        <is>
+          <t>New parallel domain node. Runs CompetitorEnricher + OccupancyEnricher. Outputs market_intel_output: competitor_pricing, area_occupancy, pricing_alerts. Writes market_assumptions dict. Participates in assumption diffing. Critic receives market context. Supersedes original P6-06.</t>
+        </is>
+      </c>
+      <c r="G25" s="54" t="inlineStr">
+        <is>
+          <t>feat: market_intel_node — 10th parallel LangGraph node, Swiggy-powered market awareness</t>
+        </is>
+      </c>
+      <c r="H25" s="54" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md (market_intel_node section), docs/ARCHITECTURE.md (11-node pipeline), docs/DECISIONS.md (D-020)</t>
+        </is>
+      </c>
+      <c r="I25" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J25" s="51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K25" s="53" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L25" s="53" t="inlineStr"/>
+      <c r="M25" s="53" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="N25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="54" t="inlineStr">
+        <is>
+          <t>P6-S10</t>
+        </is>
+      </c>
+      <c r="P25" s="54" t="inlineStr">
+        <is>
+          <t>Node writes market_intel_output + market_assumptions; parallel verified; assumption diffing fires; LangSmith trace shows node</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>P6-S12</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>feature/swiggy-dineout-manager-node</t>
+        </is>
+      </c>
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t>dineout_manager_node — 11th LangGraph node</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t>New parallel domain node. get_booking_status checks your own Dineout booking density. get_available_slots checks remaining capacity. If reservation node predicts high walk-in AND slots low → queues book_table action. Writes dineout_assumptions dict.</t>
+        </is>
+      </c>
+      <c r="G26" s="49" t="inlineStr">
+        <is>
+          <t>feat: dineout_manager_node — 11th parallel LangGraph node, manages your Dineout presence</t>
+        </is>
+      </c>
+      <c r="H26" s="49" t="inlineStr">
+        <is>
+          <t>docs/AGENTS.md (dineout_manager_node section), docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="I26" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J26" s="51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K26" s="48" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L26" s="48" t="inlineStr"/>
+      <c r="M26" s="48" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="N26" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="49" t="inlineStr">
+        <is>
+          <t>P6-S11</t>
+        </is>
+      </c>
+      <c r="P26" s="49" t="inlineStr">
+        <is>
+          <t>Writes dineout_manager_output + dineout_assumptions; book_table action queued when conditions met; LangSmith trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="6" customHeight="1">
+      <c r="A27" s="53" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B27" s="53" t="inlineStr">
+        <is>
+          <t>P6-S13</t>
+        </is>
+      </c>
+      <c r="C27" s="54" t="inlineStr">
+        <is>
+          <t>feature/swiggy-market-intel-node</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="E27" s="54" t="inlineStr">
+        <is>
+          <t>Assumption diffs 5 + 6 for new nodes</t>
+        </is>
+      </c>
+      <c r="F27" s="54" t="inlineStr">
+        <is>
+          <t>Diff 5: market_intel assumed_competitor_avg_price vs menu_intel items_assumed_available pricing. Diff 6: dineout_manager assumed_dineout_slots_low vs reservation assumed_peak_occupancy. Extends P6-00b. Total now 5 active diffs.</t>
+        </is>
+      </c>
+      <c r="G27" s="54" t="inlineStr">
+        <is>
+          <t>feat: assumption diffs 5+6 — market vs menu pricing, dineout slots vs reservation occupancy</t>
+        </is>
+      </c>
+      <c r="H27" s="54" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md (sanity checker updated), docs/AGENTS.md</t>
+        </is>
+      </c>
+      <c r="I27" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J27" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K27" s="53" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L27" s="53" t="inlineStr"/>
+      <c r="M27" s="53" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="N27" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="54" t="inlineStr">
+        <is>
+          <t>P6-S11</t>
+        </is>
+      </c>
+      <c r="P27" s="54" t="inlineStr">
+        <is>
+          <t>Diff 5 + 6 fire correctly; existing 3 diffs unaffected; stale_assumptions includes new conflicts</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1"/>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="57" t="inlineStr">
+        <is>
+          <t>WEEK 5 — Action Layer: Execution + Approval Gates</t>
+        </is>
+      </c>
+      <c r="B29" s="103" t="n"/>
+      <c r="C29" s="103" t="n"/>
+      <c r="D29" s="103" t="n"/>
+      <c r="E29" s="103" t="n"/>
+      <c r="F29" s="103" t="n"/>
+      <c r="G29" s="103" t="n"/>
+      <c r="H29" s="103" t="n"/>
+      <c r="I29" s="103" t="n"/>
+      <c r="J29" s="103" t="n"/>
+      <c r="K29" s="103" t="n"/>
+      <c r="L29" s="103" t="n"/>
+      <c r="M29" s="103" t="n"/>
+      <c r="N29" s="103" t="n"/>
+      <c r="O29" s="103" t="n"/>
+      <c r="P29" s="104" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="58" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B30" s="58" t="inlineStr">
+        <is>
+          <t>P6-S14</t>
+        </is>
+      </c>
+      <c r="C30" s="59" t="inlineStr">
+        <is>
+          <t>feature/swiggy-action-queue</t>
+        </is>
+      </c>
+      <c r="D30" s="59" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E30" s="59" t="inlineStr">
+        <is>
+          <t>ActionQueueService + action_queue table</t>
+        </is>
+      </c>
+      <c r="F30" s="59" t="inlineStr">
+        <is>
+          <t>New table: id, org_id, action_type (AUTO/APPROVE_REQUIRED/RECOMMENDATION), payload jsonb, status (PENDING/APPROVED/EXECUTED/REJECTED/EXPIRED), approved_by, executed_at, error. ActionQueueService CRUD. Plan output includes action_queue section in API response.</t>
+        </is>
+      </c>
+      <c r="G30" s="59" t="inlineStr">
+        <is>
+          <t>feat: ActionQueueService + action_queue table — 3-tier action model with approval lifecycle</t>
+        </is>
+      </c>
+      <c r="H30" s="59" t="inlineStr">
+        <is>
+          <t>docs/ACTION_QUEUE.md (new), docs/APIS.md (action queue endpoints), docs/DECISIONS.md (D-021)</t>
+        </is>
+      </c>
+      <c r="I30" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J30" s="51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K30" s="58" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L30" s="58" t="inlineStr"/>
+      <c r="M30" s="58" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="N30" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="59" t="inlineStr">
+        <is>
+          <t>P6-S10</t>
+        </is>
+      </c>
+      <c r="P30" s="59" t="inlineStr">
+        <is>
+          <t>Action CRUD tests; status transitions PENDING→APPROVED→EXECUTED; plan response includes action_queue; expired cleanup</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>P6-S15</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="inlineStr">
+        <is>
+          <t>feature/swiggy-procurement-l2</t>
+        </is>
+      </c>
+      <c r="D31" s="49" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t>ProcurementExecutor — Instamart checkout (ReAct pattern)</t>
+        </is>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
+        <is>
+          <t>ReAct-style execution (absorbs original P6-05): LLM observes search_products result, refines query if needed (max 3 iterations), selects variant. Then: get_cart → clear_cart → update_cart (spinIds) → get_cart → LangGraph interrupt() → owner approval → checkout. Check-then-retry on 5xx. procurement_orders table.</t>
+        </is>
+      </c>
+      <c r="G31" s="49" t="inlineStr">
+        <is>
+          <t>feat: ProcurementExecutor — ReAct ingredient search + Instamart checkout with approval gate</t>
+        </is>
+      </c>
+      <c r="H31" s="49" t="inlineStr">
+        <is>
+          <t>docs/ACTION_QUEUE.md (procurement flow), docs/SWIGGY_INTEGRATION.md (checkout non-idempotency)</t>
+        </is>
+      </c>
+      <c r="I31" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J31" s="51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K31" s="48" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L31" s="48" t="inlineStr"/>
+      <c r="M31" s="48" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="N31" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="49" t="inlineStr">
+        <is>
+          <t>P6-S14</t>
+        </is>
+      </c>
+      <c r="P31" s="49" t="inlineStr">
+        <is>
+          <t>ReAct max 3 iterations; check-then-retry on 5xx; interrupt() pauses graph; approval resumes checkout; procurement_orders row created</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="6" customHeight="1">
+      <c r="A32" s="58" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B32" s="58" t="inlineStr">
+        <is>
+          <t>P6-S16</t>
+        </is>
+      </c>
+      <c r="C32" s="59" t="inlineStr">
+        <is>
+          <t>feature/swiggy-action-queue</t>
+        </is>
+      </c>
+      <c r="D32" s="59" t="inlineStr">
+        <is>
+          <t>Agents</t>
+        </is>
+      </c>
+      <c r="E32" s="59" t="inlineStr">
+        <is>
+          <t>Dineout table booking execution</t>
+        </is>
+      </c>
+      <c r="F32" s="59" t="inlineStr">
+        <is>
+          <t>When dineout_manager_node queues book_table and owner approves: create_cart (DEAL_TICKET_PURCHASE) → book_table (slotId, itemId, reservationTime, guestCount, lat/lng). On 5xx: get_booking_status before retry. Confirmation written to reservations table.</t>
+        </is>
+      </c>
+      <c r="G32" s="59" t="inlineStr">
+        <is>
+          <t>feat: Dineout table booking execution with approval gate</t>
+        </is>
+      </c>
+      <c r="H32" s="59" t="inlineStr">
+        <is>
+          <t>docs/SWIGGY_INTEGRATION.md (book_table non-idempotency), docs/ACTION_QUEUE.md</t>
+        </is>
+      </c>
+      <c r="I32" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J32" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K32" s="58" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L32" s="58" t="inlineStr"/>
+      <c r="M32" s="58" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="N32" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="59" t="inlineStr">
+        <is>
+          <t>P6-S14</t>
+        </is>
+      </c>
+      <c r="P32" s="59" t="inlineStr">
+        <is>
+          <t>Non-idempotent retry test; end-to-end approval flow; confirmation in reservations table; rejection has no side effects</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1"/>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="61" t="inlineStr">
+        <is>
+          <t>WEEK 6 — Product Modes: Brief, Live, MCP Expansion</t>
+        </is>
+      </c>
+      <c r="B34" s="103" t="n"/>
+      <c r="C34" s="103" t="n"/>
+      <c r="D34" s="103" t="n"/>
+      <c r="E34" s="103" t="n"/>
+      <c r="F34" s="103" t="n"/>
+      <c r="G34" s="103" t="n"/>
+      <c r="H34" s="103" t="n"/>
+      <c r="I34" s="103" t="n"/>
+      <c r="J34" s="103" t="n"/>
+      <c r="K34" s="103" t="n"/>
+      <c r="L34" s="103" t="n"/>
+      <c r="M34" s="103" t="n"/>
+      <c r="N34" s="103" t="n"/>
+      <c r="O34" s="103" t="n"/>
+      <c r="P34" s="104" t="n"/>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="62" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B35" s="62" t="inlineStr">
+        <is>
+          <t>P6-S17</t>
+        </is>
+      </c>
+      <c r="C35" s="63" t="inlineStr">
+        <is>
+          <t>feature/swiggy-brief-mode</t>
+        </is>
+      </c>
+      <c r="D35" s="63" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E35" s="63" t="inlineStr">
+        <is>
+          <t>BriefingService — automated 7am daily brief</t>
+        </is>
+      </c>
+      <c r="F35" s="63" t="inlineStr">
+        <is>
+          <t>APScheduler job at 07:00 IST per org. Lightweight run: demand_forecast + market_intel_node only. Pulls overnight Swiggy signals (get_food_orders since last run, track_food_order performance). Generates daily_brief JSON. Stores in daily_briefs table. Email digest (extends P5-11).</t>
+        </is>
+      </c>
+      <c r="G35" s="63" t="inlineStr">
+        <is>
+          <t>feat: BriefingService — automated daily morning brief with overnight Swiggy signals</t>
+        </is>
+      </c>
+      <c r="H35" s="63" t="inlineStr">
+        <is>
+          <t>docs/PRODUCT_MODES.md (new, brief mode), docs/APIS.md (brief endpoints)</t>
+        </is>
+      </c>
+      <c r="I35" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J35" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K35" s="62" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L35" s="62" t="inlineStr"/>
+      <c r="M35" s="62" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="N35" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="63" t="inlineStr">
+        <is>
+          <t>P6-S10</t>
+        </is>
+      </c>
+      <c r="P35" s="63" t="inlineStr">
+        <is>
+          <t>Scheduler fires at correct time; brief generates without full pipeline; daily_briefs row created; email sends</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="52" customHeight="1">
+      <c r="A36" s="48" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>P6-S18</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="inlineStr">
+        <is>
+          <t>feature/swiggy-live-mode</t>
+        </is>
+      </c>
+      <c r="D36" s="49" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E36" s="49" t="inlineStr">
+        <is>
+          <t>LiveMonitorService — real-time during service hours</t>
+        </is>
+      </c>
+      <c r="F36" s="49" t="inlineStr">
+        <is>
+          <t>SSE feed during service hours (12:00-14:00, 19:00-22:00 IST). Polls every 30s: get_food_orders (active), track_food_order (in-flight), track_order (Instamart procurement). Alerts: delivery &gt; threshold, order spike, ingredient arrived. Stops outside service window.</t>
+        </is>
+      </c>
+      <c r="G36" s="49" t="inlineStr">
+        <is>
+          <t>feat: LiveMonitorService — real-time SSE ops monitor during service hours</t>
+        </is>
+      </c>
+      <c r="H36" s="49" t="inlineStr">
+        <is>
+          <t>docs/PRODUCT_MODES.md (live mode section), docs/APIS.md (live SSE endpoint)</t>
+        </is>
+      </c>
+      <c r="I36" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J36" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K36" s="48" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L36" s="48" t="inlineStr"/>
+      <c r="M36" s="48" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="N36" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="49" t="inlineStr">
+        <is>
+          <t>P6-S15</t>
+        </is>
+      </c>
+      <c r="P36" s="49" t="inlineStr">
+        <is>
+          <t>SSE events fire; 30s poll verified; alerts trigger correctly; stops outside service hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="6" customHeight="1">
+      <c r="A37" s="62" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B37" s="62" t="inlineStr">
+        <is>
+          <t>P6-S19</t>
+        </is>
+      </c>
+      <c r="C37" s="63" t="inlineStr">
+        <is>
+          <t>feature/swiggy-mcp-tools</t>
+        </is>
+      </c>
+      <c r="D37" s="63" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="E37" s="63" t="inlineStr">
+        <is>
+          <t>3 new CortexKitchen MCP server tools</t>
+        </is>
+      </c>
+      <c r="F37" s="63" t="inlineStr">
+        <is>
+          <t>Add to mcp_server.py: get_market_brief (calls MarketIntelService live, returns competitor snapshot for Claude Desktop), get_action_queue (pending actions awaiting approval), approve_action (owner approves from Claude Desktop, triggers execution). JWT auth on all 3.</t>
+        </is>
+      </c>
+      <c r="G37" s="63" t="inlineStr">
+        <is>
+          <t>feat: 3 new MCP tools — get_market_brief, get_action_queue, approve_action</t>
+        </is>
+      </c>
+      <c r="H37" s="63" t="inlineStr">
+        <is>
+          <t>docs/APIS.md (MCP tools section), docs/ARCHITECTURE.md (MCP server updated)</t>
+        </is>
+      </c>
+      <c r="I37" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J37" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K37" s="62" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L37" s="62" t="inlineStr"/>
+      <c r="M37" s="62" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="N37" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="63" t="inlineStr">
+        <is>
+          <t>P6-S14</t>
+        </is>
+      </c>
+      <c r="P37" s="63" t="inlineStr">
+        <is>
+          <t>All 3 tools smoke-tested in Claude Desktop; approve_action triggers execution end-to-end; JWT enforced</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1"/>
+    <row r="39" ht="52" customHeight="1">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>WEEK 6-7 — Original P6 Tasks (POS Connector + Voice)</t>
+        </is>
+      </c>
+      <c r="B39" s="103" t="n"/>
+      <c r="C39" s="103" t="n"/>
+      <c r="D39" s="103" t="n"/>
+      <c r="E39" s="103" t="n"/>
+      <c r="F39" s="103" t="n"/>
+      <c r="G39" s="103" t="n"/>
+      <c r="H39" s="103" t="n"/>
+      <c r="I39" s="103" t="n"/>
+      <c r="J39" s="103" t="n"/>
+      <c r="K39" s="103" t="n"/>
+      <c r="L39" s="103" t="n"/>
+      <c r="M39" s="103" t="n"/>
+      <c r="N39" s="103" t="n"/>
+      <c r="O39" s="103" t="n"/>
+      <c r="P39" s="104" t="n"/>
+    </row>
+    <row r="40" ht="52" customHeight="1">
+      <c r="A40" s="65" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B40" s="65" t="inlineStr">
+        <is>
+          <t>P6-R01</t>
+        </is>
+      </c>
+      <c r="C40" s="66" t="inlineStr">
+        <is>
+          <t>feature/swiggy-pos-connector</t>
+        </is>
+      </c>
+      <c r="D40" s="66" t="inlineStr">
         <is>
           <t>Integrations</t>
         </is>
       </c>
-      <c r="E15" s="44" t="inlineStr">
-        <is>
-          <t>Sync delivery performance → feedback table</t>
-        </is>
-      </c>
-      <c r="F15" s="44" t="inlineStr">
-        <is>
-          <t>track_food_order → feedback rows: source='swiggy_delivery', prep_time_actual, delivery_time_actual, promised_time, late_flag. ComplaintService surfaces delivery latency patterns. RAG runs over real delivery feedback in Qdrant.</t>
-        </is>
-      </c>
-      <c r="G15" s="44" t="inlineStr">
-        <is>
-          <t>feat: swiggy delivery signal sync — track_food_order → feedback table (source=swiggy_delivery)</t>
-        </is>
-      </c>
-      <c r="H15" s="44" t="inlineStr">
-        <is>
-          <t>docs/DATA_SOURCES.md (delivery feedback), docs/AGENTS.md (complaint_intel updated)</t>
-        </is>
-      </c>
-      <c r="I15" s="45" t="inlineStr">
+      <c r="E40" s="66" t="inlineStr">
+        <is>
+          <t>POS connector — Square/Toast CSV (2nd connector)</t>
+        </is>
+      </c>
+      <c r="F40" s="66" t="inlineStr">
+        <is>
+          <t>Second implementation of BaseConnector. CSV import from Square/Toast export. Maps dine-in orders to orders table with source='pos', channel='dine_in'. Dedup by external_order_id. Validates against InventoryService and ForecastService. Now ForecastService has both delivery (Swiggy) and dine-in (POS) channels.</t>
+        </is>
+      </c>
+      <c r="G40" s="66" t="inlineStr">
+        <is>
+          <t>feat: POSConnector — Square/Toast CSV import, source=pos, channel=dine_in</t>
+        </is>
+      </c>
+      <c r="H40" s="66" t="inlineStr">
+        <is>
+          <t>docs/CONNECTORS.md (POSConnector section), docs/DATA_SOURCES.md (POS section)</t>
+        </is>
+      </c>
+      <c r="I40" s="45" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J15" s="51" t="inlineStr">
+      <c r="J40" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K40" s="65" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L40" s="65" t="inlineStr"/>
+      <c r="M40" s="65" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="N40" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="66" t="inlineStr">
+        <is>
+          <t>P6-S03</t>
+        </is>
+      </c>
+      <c r="P40" s="66" t="inlineStr">
+        <is>
+          <t>CSV import unit tests; ForecastService integration with both channels; dedup test; InventoryService validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="6" customHeight="1">
+      <c r="A41" s="48" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B41" s="48" t="inlineStr">
+        <is>
+          <t>P6-R02</t>
+        </is>
+      </c>
+      <c r="C41" s="49" t="inlineStr">
+        <is>
+          <t>feature/swiggy-voice-interface</t>
+        </is>
+      </c>
+      <c r="D41" s="49" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="E41" s="49" t="inlineStr">
+        <is>
+          <t>Voice interface — Whisper + RAG chatbot</t>
+        </is>
+      </c>
+      <c r="F41" s="49" t="inlineStr">
+        <is>
+          <t>Whisper transcription on browser-recorded question (MediaRecorder API). RAG chatbot (P5-12) answers. TTS reads back. Manager asks questions while walking the floor. Works with both synthetic and real Swiggy data now in DB. Blocked on P5-12 (already done).</t>
+        </is>
+      </c>
+      <c r="G41" s="49" t="inlineStr">
+        <is>
+          <t>feat: voice interface — Whisper transcription + RAG answer + TTS readback</t>
+        </is>
+      </c>
+      <c r="H41" s="49" t="inlineStr">
+        <is>
+          <t>docs/PRODUCT_MODES.md (voice section)</t>
+        </is>
+      </c>
+      <c r="I41" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J41" s="45" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K41" s="48" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L41" s="48" t="inlineStr"/>
+      <c r="M41" s="48" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="N41" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="49" t="inlineStr">
+        <is>
+          <t>P6-S16</t>
+        </is>
+      </c>
+      <c r="P41" s="49" t="inlineStr">
+        <is>
+          <t>Transcription accuracy smoke test; end-to-end voice → RAG answer → TTS; works with real Swiggy data in DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1"/>
+    <row r="43" ht="52" customHeight="1">
+      <c r="A43" s="42" t="inlineStr">
+        <is>
+          <t>WEEK 7 — Frontend: 5 New Pages + 3 New Panels</t>
+        </is>
+      </c>
+      <c r="B43" s="103" t="n"/>
+      <c r="C43" s="103" t="n"/>
+      <c r="D43" s="103" t="n"/>
+      <c r="E43" s="103" t="n"/>
+      <c r="F43" s="103" t="n"/>
+      <c r="G43" s="103" t="n"/>
+      <c r="H43" s="103" t="n"/>
+      <c r="I43" s="103" t="n"/>
+      <c r="J43" s="103" t="n"/>
+      <c r="K43" s="103" t="n"/>
+      <c r="L43" s="103" t="n"/>
+      <c r="M43" s="103" t="n"/>
+      <c r="N43" s="103" t="n"/>
+      <c r="O43" s="103" t="n"/>
+      <c r="P43" s="104" t="n"/>
+    </row>
+    <row r="44" ht="52" customHeight="1">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>P6-F01</t>
+        </is>
+      </c>
+      <c r="C44" s="44" t="inlineStr">
+        <is>
+          <t>feature/swiggy-frontend-market</t>
+        </is>
+      </c>
+      <c r="D44" s="44" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E44" s="44" t="inlineStr">
+        <is>
+          <t>Market intelligence panel (planning results page)</t>
+        </is>
+      </c>
+      <c r="F44" s="44" t="inlineStr">
+        <is>
+          <t>New panel on /runs/{id}. Competitor pricing table: your price vs area avg vs cheapest competitor per dish category. Area occupancy badge (HIGH/MEDIUM/LOW). Instamart prices for shortage items. Pricing alerts (red if &gt;20% above area avg). Hidden when market_intel_output absent.</t>
+        </is>
+      </c>
+      <c r="G44" s="44" t="inlineStr">
+        <is>
+          <t>feat: market intelligence panel — competitor pricing + area occupancy on planning results</t>
+        </is>
+      </c>
+      <c r="H44" s="44" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="I44" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J44" s="51" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K15" s="43" t="inlineStr">
+      <c r="K44" s="43" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L15" s="43" t="inlineStr"/>
-      <c r="M15" s="43" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="N15" s="47" t="n">
+      <c r="L44" s="43" t="inlineStr"/>
+      <c r="M44" s="43" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="N44" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="44" t="inlineStr">
-        <is>
-          <t>P6-S03</t>
-        </is>
-      </c>
-      <c r="P15" s="44" t="inlineStr">
-        <is>
-          <t>Latency mapping test; late_flag logic; ComplaintService source filter; RAG retrieval returns real delivery complaints</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="6" customHeight="1"/>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="52" t="inlineStr">
-        <is>
-          <t>WEEK 3 — Market Intelligence: Live Enrichment</t>
-        </is>
-      </c>
-      <c r="B17" s="103" t="n"/>
-      <c r="C17" s="103" t="n"/>
-      <c r="D17" s="103" t="n"/>
-      <c r="E17" s="103" t="n"/>
-      <c r="F17" s="103" t="n"/>
-      <c r="G17" s="103" t="n"/>
-      <c r="H17" s="103" t="n"/>
-      <c r="I17" s="103" t="n"/>
-      <c r="J17" s="103" t="n"/>
-      <c r="K17" s="103" t="n"/>
-      <c r="L17" s="103" t="n"/>
-      <c r="M17" s="103" t="n"/>
-      <c r="N17" s="103" t="n"/>
-      <c r="O17" s="103" t="n"/>
-      <c r="P17" s="104" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="53" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B18" s="53" t="inlineStr">
-        <is>
-          <t>P6-S06</t>
-        </is>
-      </c>
-      <c r="C18" s="54" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-enrichers</t>
-        </is>
-      </c>
-      <c r="D18" s="54" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="E18" s="54" t="inlineStr">
-        <is>
-          <t>CompetitorEnricher — Food MCP</t>
-        </is>
-      </c>
-      <c r="F18" s="54" t="inlineStr">
-        <is>
-          <t>search_restaurants (cuisine, addressId) → filter OPEN → search_menu + get_restaurant_menu per restaurant (max 3) → competitor_pricing dict: area avg price per dish category, pricing alerts vs your menu. Redis cache 30min TTL. Supersedes original P6-07 (no scraping needed).</t>
-        </is>
-      </c>
-      <c r="G18" s="54" t="inlineStr">
-        <is>
-          <t>feat: CompetitorEnricher — live competitor pricing via Food MCP</t>
-        </is>
-      </c>
-      <c r="H18" s="54" t="inlineStr">
-        <is>
-          <t>docs/SWIGGY_INTEGRATION.md (new, CompetitorEnricher section), docs/AGENTS.md (menu_intel updated)</t>
-        </is>
-      </c>
-      <c r="I18" s="45" t="inlineStr">
+      <c r="O44" s="44" t="inlineStr">
+        <is>
+          <t>P6-S10</t>
+        </is>
+      </c>
+      <c r="P44" s="44" t="inlineStr">
+        <is>
+          <t>Panel renders when data present; hides gracefully when not; pricing alerts correct; occupancy badge correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="52" customHeight="1">
+      <c r="A45" s="48" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B45" s="48" t="inlineStr">
+        <is>
+          <t>P6-F02</t>
+        </is>
+      </c>
+      <c r="C45" s="49" t="inlineStr">
+        <is>
+          <t>feature/swiggy-frontend-actions</t>
+        </is>
+      </c>
+      <c r="D45" s="49" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E45" s="49" t="inlineStr">
+        <is>
+          <t>Action queue UI + procurement tracker</t>
+        </is>
+      </c>
+      <c r="F45" s="49" t="inlineStr">
+        <is>
+          <t>New section below plan output. Lists pending actions with type badge. Approve/Reject buttons for APPROVE_REQUIRED. Instamart cart preview modal (items, total, ETA) before approving checkout. Procurement tracker in inventory panel: placed orders, status, ETA.</t>
+        </is>
+      </c>
+      <c r="G45" s="49" t="inlineStr">
+        <is>
+          <t>feat: action queue UI — approve/reject with cart preview, procurement tracker</t>
+        </is>
+      </c>
+      <c r="H45" s="49" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="I45" s="45" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J18" s="51" t="inlineStr">
+      <c r="J45" s="51" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K18" s="53" t="inlineStr">
+      <c r="K45" s="48" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L18" s="53" t="inlineStr"/>
-      <c r="M18" s="53" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="N18" s="55" t="n">
+      <c r="L45" s="48" t="inlineStr"/>
+      <c r="M45" s="48" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="N45" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="54" t="inlineStr">
-        <is>
-          <t>P6-S02</t>
-        </is>
-      </c>
-      <c r="P18" s="54" t="inlineStr">
-        <is>
-          <t>Structured dict with area_avg_price; graceful None on failure; Redis cache hit; menu_intel prompt includes market context</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="48" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B19" s="48" t="inlineStr">
-        <is>
-          <t>P6-S07</t>
-        </is>
-      </c>
-      <c r="C19" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-enrichers</t>
-        </is>
-      </c>
-      <c r="D19" s="49" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="E19" s="49" t="inlineStr">
-        <is>
-          <t>OccupancyEnricher — Dineout MCP</t>
-        </is>
-      </c>
-      <c r="F19" s="49" t="inlineStr">
-        <is>
-          <t>get_saved_locations → search_restaurants_dineout → get_restaurant_details (top 3) → get_available_slots (today) → occupancy_signal: HIGH/MEDIUM/LOW, tonight_busy bool. Redis cache 30min TTL. Supersedes original P6-06 Google Trends approach.</t>
-        </is>
-      </c>
-      <c r="G19" s="49" t="inlineStr">
-        <is>
-          <t>feat: OccupancyEnricher — live competitor occupancy via Dineout MCP</t>
-        </is>
-      </c>
-      <c r="H19" s="49" t="inlineStr">
-        <is>
-          <t>docs/SWIGGY_INTEGRATION.md (OccupancyEnricher section), docs/AGENTS.md (reservation updated)</t>
-        </is>
-      </c>
-      <c r="I19" s="45" t="inlineStr">
+      <c r="O45" s="49" t="inlineStr">
+        <is>
+          <t>P6-S13</t>
+        </is>
+      </c>
+      <c r="P45" s="49" t="inlineStr">
+        <is>
+          <t>Action list renders; approve triggers API; cart preview correct; reject has no side effects; tracker updates on delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="52" customHeight="1">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>P6-F03</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>feature/swiggy-frontend-brief</t>
+        </is>
+      </c>
+      <c r="D46" s="44" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E46" s="44" t="inlineStr">
+        <is>
+          <t>/brief page — daily morning briefing</t>
+        </is>
+      </c>
+      <c r="F46" s="44" t="inlineStr">
+        <is>
+          <t>New route /brief. Overnight Swiggy performance (orders, avg delivery time, late %), today's demand forecast vs yesterday, top 3 action priorities, market snapshot. Auto-refreshes if brief is stale. Empty state when no brief yet.</t>
+        </is>
+      </c>
+      <c r="G46" s="44" t="inlineStr">
+        <is>
+          <t>feat: /brief page — daily morning operational briefing</t>
+        </is>
+      </c>
+      <c r="H46" s="44" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="I46" s="45" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J19" s="51" t="inlineStr">
+      <c r="J46" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K46" s="43" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L46" s="43" t="inlineStr"/>
+      <c r="M46" s="43" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="N46" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="44" t="inlineStr">
+        <is>
+          <t>P6-S16</t>
+        </is>
+      </c>
+      <c r="P46" s="44" t="inlineStr">
+        <is>
+          <t>Page loads; stale brief triggers refresh; all 4 sections render; empty state works</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="52" customHeight="1">
+      <c r="A47" s="48" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B47" s="48" t="inlineStr">
+        <is>
+          <t>P6-F04</t>
+        </is>
+      </c>
+      <c r="C47" s="49" t="inlineStr">
+        <is>
+          <t>feature/swiggy-frontend-connectors</t>
+        </is>
+      </c>
+      <c r="D47" s="49" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E47" s="49" t="inlineStr">
+        <is>
+          <t>/connectors page — data source management</t>
+        </is>
+      </c>
+      <c r="F47" s="49" t="inlineStr">
+        <is>
+          <t>New route /connectors. Lists connectors with status badges (Connected/Disconnected/Error). Shows last sync time, records synced, data freshness. Connect button triggers OAuth flow. Disconnect revokes token. Error state shows last error + reconnect. Works for Swiggy + future POS connector.</t>
+        </is>
+      </c>
+      <c r="G47" s="49" t="inlineStr">
+        <is>
+          <t>feat: /connectors page — platform data source management with OAuth connect flow</t>
+        </is>
+      </c>
+      <c r="H47" s="49" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="I47" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J47" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K47" s="48" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L47" s="48" t="inlineStr"/>
+      <c r="M47" s="48" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="N47" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="49" t="inlineStr">
+        <is>
+          <t>P6-S01</t>
+        </is>
+      </c>
+      <c r="P47" s="49" t="inlineStr">
+        <is>
+          <t>Connect triggers OAuth; post-OAuth shows Connected; Disconnect revokes; error state renders; POS connector appears as available</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="52" customHeight="1">
+      <c r="A48" s="43" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B48" s="43" t="inlineStr">
+        <is>
+          <t>P6-F05</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>feature/swiggy-frontend-live</t>
+        </is>
+      </c>
+      <c r="D48" s="44" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E48" s="44" t="inlineStr">
+        <is>
+          <t>/live page — real-time ops monitor</t>
+        </is>
+      </c>
+      <c r="F48" s="44" t="inlineStr">
+        <is>
+          <t>New route /live. Active during service hours (countdown outside). SSE feed: active Swiggy orders + ETA, delivery performance gauge (green/amber/red), Instamart procurement in-flight status, alert feed (last 10). Auto-connects SSE on load.</t>
+        </is>
+      </c>
+      <c r="G48" s="44" t="inlineStr">
+        <is>
+          <t>feat: /live page — real-time service-hours ops monitor via SSE</t>
+        </is>
+      </c>
+      <c r="H48" s="44" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="I48" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J48" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K48" s="43" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L48" s="43" t="inlineStr"/>
+      <c r="M48" s="43" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="N48" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="44" t="inlineStr">
+        <is>
+          <t>P6-S17</t>
+        </is>
+      </c>
+      <c r="P48" s="44" t="inlineStr">
+        <is>
+          <t>SSE connects; events update UI; countdown outside hours; gauge updates; alert feed shows last 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="6" customHeight="1">
+      <c r="A49" s="48" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B49" s="48" t="inlineStr">
+        <is>
+          <t>P6-F06</t>
+        </is>
+      </c>
+      <c r="C49" s="49" t="inlineStr">
+        <is>
+          <t>feature/swiggy-frontend-market</t>
+        </is>
+      </c>
+      <c r="D49" s="49" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E49" s="49" t="inlineStr">
+        <is>
+          <t>Dashboard enhancements</t>
+        </is>
+      </c>
+      <c r="F49" s="49" t="inlineStr">
+        <is>
+          <t>Add to existing dashboard: connector status widget (data source health bar), brief mode trigger button, today's Swiggy KPIs (orders today, delivery rating, top Swiggy seller), data_sources column on /runs list.</t>
+        </is>
+      </c>
+      <c r="G49" s="49" t="inlineStr">
+        <is>
+          <t>feat: dashboard — connector status widget, brief trigger, live Swiggy KPIs, data_sources on runs list</t>
+        </is>
+      </c>
+      <c r="H49" s="49" t="inlineStr">
+        <is>
+          <t>None (frontend only)</t>
+        </is>
+      </c>
+      <c r="I49" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J49" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K49" s="48" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L49" s="48" t="inlineStr"/>
+      <c r="M49" s="48" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="N49" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="49" t="inlineStr">
+        <is>
+          <t>P6-S16</t>
+        </is>
+      </c>
+      <c r="P49" s="49" t="inlineStr">
+        <is>
+          <t>Connector widget shows status; brief trigger fires; Swiggy KPIs render; runs list data_sources column correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1"/>
+    <row r="51" ht="52" customHeight="1">
+      <c r="A51" s="61" t="inlineStr">
+        <is>
+          <t>WEEK 8 — Docs + Merge: Phase 6 Complete</t>
+        </is>
+      </c>
+      <c r="B51" s="103" t="n"/>
+      <c r="C51" s="103" t="n"/>
+      <c r="D51" s="103" t="n"/>
+      <c r="E51" s="103" t="n"/>
+      <c r="F51" s="103" t="n"/>
+      <c r="G51" s="103" t="n"/>
+      <c r="H51" s="103" t="n"/>
+      <c r="I51" s="103" t="n"/>
+      <c r="J51" s="103" t="n"/>
+      <c r="K51" s="103" t="n"/>
+      <c r="L51" s="103" t="n"/>
+      <c r="M51" s="103" t="n"/>
+      <c r="N51" s="103" t="n"/>
+      <c r="O51" s="103" t="n"/>
+      <c r="P51" s="104" t="n"/>
+    </row>
+    <row r="52" ht="52" customHeight="1">
+      <c r="A52" s="62" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B52" s="62" t="inlineStr">
+        <is>
+          <t>P6-D01</t>
+        </is>
+      </c>
+      <c r="C52" s="63" t="inlineStr">
+        <is>
+          <t>feature/swiggy-docs</t>
+        </is>
+      </c>
+      <c r="D52" s="63" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="E52" s="63" t="inlineStr">
+        <is>
+          <t>5 new documentation files</t>
+        </is>
+      </c>
+      <c r="F52" s="63" t="inlineStr">
+        <is>
+          <t>CONNECTORS.md: BaseConnector interface, sync vs enrich, how to add new connector. SWIGGY_INTEGRATION.md: all 22 tools, parameter mappings, OAuth, rate limits, error handling. ACTION_QUEUE.md: action types, approval flow, non-idempotent patterns. DATA_SOURCES.md: all sources, channels, sync frequency. PRODUCT_MODES.md: ops/brief/live/voice mode specs.</t>
+        </is>
+      </c>
+      <c r="G52" s="63" t="inlineStr">
+        <is>
+          <t>docs: 5 new documentation files for Phase 6 connector + action + product mode layer</t>
+        </is>
+      </c>
+      <c r="H52" s="63" t="inlineStr">
+        <is>
+          <t>docs/CONNECTORS.md, docs/SWIGGY_INTEGRATION.md, docs/ACTION_QUEUE.md, docs/DATA_SOURCES.md, docs/PRODUCT_MODES.md</t>
+        </is>
+      </c>
+      <c r="I52" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J52" s="51" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K19" s="48" t="inlineStr">
+      <c r="K52" s="62" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L19" s="48" t="inlineStr"/>
-      <c r="M19" s="48" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="N19" s="50" t="n">
+      <c r="L52" s="62" t="inlineStr"/>
+      <c r="M52" s="62" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="N52" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="49" t="inlineStr">
-        <is>
-          <t>P6-S06</t>
-        </is>
-      </c>
-      <c r="P19" s="49" t="inlineStr">
-        <is>
-          <t>HIGH/MEDIUM/LOW logic test; graceful None; reservation node prompt includes occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="53" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B20" s="53" t="inlineStr">
-        <is>
-          <t>P6-S08</t>
-        </is>
-      </c>
-      <c r="C20" s="54" t="inlineStr">
-        <is>
-          <t>feature/swiggy-procurement-l1</t>
-        </is>
-      </c>
-      <c r="D20" s="54" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="E20" s="54" t="inlineStr">
-        <is>
-          <t>ProcurementEnricher — Instamart (read-only)</t>
-        </is>
-      </c>
-      <c r="F20" s="54" t="inlineStr">
-        <is>
-          <t>For each shortage_alert item: search_products (addressId, ingredient) → spinId, price, unit, availability. Also your_go_to_items for frequent reorder suggestions. procurement_options dict injected into inventory node prompt. spinId stored for later execution.</t>
-        </is>
-      </c>
-      <c r="G20" s="54" t="inlineStr">
-        <is>
-          <t>feat: ProcurementEnricher — live Instamart ingredient pricing injected into inventory node</t>
-        </is>
-      </c>
-      <c r="H20" s="54" t="inlineStr">
-        <is>
-          <t>docs/SWIGGY_INTEGRATION.md (ProcurementEnricher section), docs/AGENTS.md (inventory updated)</t>
-        </is>
-      </c>
-      <c r="I20" s="45" t="inlineStr">
+      <c r="O52" s="63" t="inlineStr">
+        <is>
+          <t>P6-F06</t>
+        </is>
+      </c>
+      <c r="P52" s="63" t="inlineStr">
+        <is>
+          <t>All 5 files present; no broken links; tool parameter tables accurate vs Swiggy docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="52" customHeight="1">
+      <c r="A53" s="48" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B53" s="48" t="inlineStr">
+        <is>
+          <t>P6-D02</t>
+        </is>
+      </c>
+      <c r="C53" s="49" t="inlineStr">
+        <is>
+          <t>feature/swiggy-docs</t>
+        </is>
+      </c>
+      <c r="D53" s="49" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="E53" s="49" t="inlineStr">
+        <is>
+          <t>Update 8 existing docs</t>
+        </is>
+      </c>
+      <c r="F53" s="49" t="inlineStr">
+        <is>
+          <t>ARCHITECTURE.md: connector layer, 11-node pipeline, action layer, product modes. AGENTS.md: 2 new nodes + 2 new diffs. APIS.md: all new endpoints. DATA_MODEL.md: 6 new tables. DECISIONS.md: D-019 through D-022. ROADMAP.md: Phase 6 in-progress. EVALUATION.md: new node eval criteria. README.md: updated product headline.</t>
+        </is>
+      </c>
+      <c r="G53" s="49" t="inlineStr">
+        <is>
+          <t>docs: update 8 existing docs to reflect full Phase 6 additions</t>
+        </is>
+      </c>
+      <c r="H53" s="49" t="inlineStr">
+        <is>
+          <t>ARCHITECTURE, AGENTS, APIS, DATA_MODEL, DECISIONS, ROADMAP, EVALUATION, README</t>
+        </is>
+      </c>
+      <c r="I53" s="45" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J20" s="51" t="inlineStr">
+      <c r="J53" s="51" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K20" s="53" t="inlineStr">
+      <c r="K53" s="48" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L20" s="53" t="inlineStr"/>
-      <c r="M20" s="53" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="N20" s="55" t="n">
+      <c r="L53" s="48" t="inlineStr"/>
+      <c r="M53" s="48" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="N53" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="54" t="inlineStr">
-        <is>
-          <t>P6-S06</t>
-        </is>
-      </c>
-      <c r="P20" s="54" t="inlineStr">
-        <is>
-          <t>procurement_options per shortage item; spinId captured; graceful None; inventory prompt includes live prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="48" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B21" s="48" t="inlineStr">
-        <is>
-          <t>P6-S09</t>
-        </is>
-      </c>
-      <c r="C21" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-enrichers</t>
-        </is>
-      </c>
-      <c r="D21" s="49" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="E21" s="49" t="inlineStr">
-        <is>
-          <t>MarketIntelService + 6 new OrchestratorState fields</t>
-        </is>
-      </c>
-      <c r="F21" s="49" t="inlineStr">
-        <is>
-          <t>MarketIntelService orchestrates all 3 enrichers. Adds 6 Annotated[Optional[Dict], keep_last] fields to OrchestratorState: swiggy_competitor_context, swiggy_occupancy_context, swiggy_procurement_options, swiggy_delivery_signal, market_intel_output, dineout_manager_output.</t>
-        </is>
-      </c>
-      <c r="G21" s="49" t="inlineStr">
-        <is>
-          <t>feat: MarketIntelService + 6 new OrchestratorState enrichment fields</t>
-        </is>
-      </c>
-      <c r="H21" s="49" t="inlineStr">
-        <is>
-          <t>docs/ARCHITECTURE.md (MarketIntelService), docs/DATA_MODEL.md (state fields)</t>
-        </is>
-      </c>
-      <c r="I21" s="45" t="inlineStr">
+      <c r="O53" s="49" t="inlineStr">
+        <is>
+          <t>P6-D01</t>
+        </is>
+      </c>
+      <c r="P53" s="49" t="inlineStr">
+        <is>
+          <t>No stale 9-node pipeline references; all new endpoints in APIS.md; D-019 through D-022 in DECISIONS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="6" customHeight="1">
+      <c r="A54" s="62" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B54" s="62" t="inlineStr">
+        <is>
+          <t>P6-D03</t>
+        </is>
+      </c>
+      <c r="C54" s="63" t="inlineStr">
+        <is>
+          <t>dev -&gt; main PR</t>
+        </is>
+      </c>
+      <c r="D54" s="63" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="E54" s="63" t="inlineStr">
+        <is>
+          <t>Phase 6 milestone merge to main</t>
+        </is>
+      </c>
+      <c r="F54" s="63" t="inlineStr">
+        <is>
+          <t>Merge feature/ck-v2-platform → dev → main. All 11 nodes verified in LangSmith. All 22 Swiggy tools exercised in staging. POS connector imports CSV end-to-end. Voice interface smoke tested. Action queue end-to-end. All 3 product modes verified. 5 new frontend pages smoke tested. Full test suite green.</t>
+        </is>
+      </c>
+      <c r="G54" s="63" t="inlineStr">
+        <is>
+          <t>release: Phase 6 complete — CortexKitchen v2 Swiggy-native restaurant OS</t>
+        </is>
+      </c>
+      <c r="H54" s="63" t="inlineStr">
+        <is>
+          <t>README.md (portfolio headline), docs/ROADMAP.md (Phase 6 complete)</t>
+        </is>
+      </c>
+      <c r="I54" s="45" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J21" s="51" t="inlineStr">
+      <c r="J54" s="46" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K54" s="62" t="inlineStr">
+        <is>
+          <t>Anoushka</t>
+        </is>
+      </c>
+      <c r="L54" s="62" t="inlineStr"/>
+      <c r="M54" s="62" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="N54" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="63" t="inlineStr">
+        <is>
+          <t>P6-D02</t>
+        </is>
+      </c>
+      <c r="P54" s="63" t="inlineStr">
+        <is>
+          <t>Full test suite green; 11 nodes in LangSmith; staging demo clean; portfolio README updated; docs website prep checklist done</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1"/>
+    <row r="56" ht="52" customHeight="1">
+      <c r="A56" s="68" t="inlineStr">
+        <is>
+          <t>PHASE 7 — Production, CI/CD, Docs Website</t>
+        </is>
+      </c>
+      <c r="B56" s="103" t="n"/>
+      <c r="C56" s="103" t="n"/>
+      <c r="D56" s="103" t="n"/>
+      <c r="E56" s="103" t="n"/>
+      <c r="F56" s="103" t="n"/>
+      <c r="G56" s="103" t="n"/>
+      <c r="H56" s="103" t="n"/>
+      <c r="I56" s="103" t="n"/>
+      <c r="J56" s="103" t="n"/>
+      <c r="K56" s="103" t="n"/>
+      <c r="L56" s="103" t="n"/>
+      <c r="M56" s="103" t="n"/>
+      <c r="N56" s="103" t="n"/>
+      <c r="O56" s="103" t="n"/>
+      <c r="P56" s="104" t="n"/>
+    </row>
+    <row r="57" ht="52" customHeight="1">
+      <c r="A57" s="69" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="B57" s="69" t="inlineStr">
+        <is>
+          <t>P7-01</t>
+        </is>
+      </c>
+      <c r="C57" s="70" t="inlineStr">
+        <is>
+          <t>feature/phase7-cicd</t>
+        </is>
+      </c>
+      <c r="D57" s="70" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="E57" s="70" t="inlineStr">
+        <is>
+          <t>CI/CD — GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F57" s="70" t="inlineStr">
+        <is>
+          <t>Automated on every PR: unit + integration + RAGAS evals + DeepEval; lint; type check; frontend build; coverage report. Fail on critic score regression. Cache pip dependencies.</t>
+        </is>
+      </c>
+      <c r="G57" s="70" t="inlineStr">
+        <is>
+          <t>feat: CI/CD — automated test + eval pipeline on every PR</t>
+        </is>
+      </c>
+      <c r="H57" s="70" t="inlineStr">
+        <is>
+          <t>docs/ROADMAP.md</t>
+        </is>
+      </c>
+      <c r="I57" s="45" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="J57" s="51" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K21" s="48" t="inlineStr">
+      <c r="K57" s="69" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L21" s="48" t="inlineStr"/>
-      <c r="M21" s="48" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="N21" s="50" t="n">
+      <c r="L57" s="69" t="inlineStr"/>
+      <c r="M57" s="69" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="N57" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="49" t="inlineStr">
-        <is>
-          <t>P6-S06</t>
-        </is>
-      </c>
-      <c r="P21" s="49" t="inlineStr">
-        <is>
-          <t>State field type tests; MarketIntelService runs all 3 enrichers; final_assembler passes through</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="52" t="inlineStr">
-        <is>
-          <t>WEEK 4 — New Nodes: Pipeline Expands to 11 Nodes</t>
-        </is>
-      </c>
-      <c r="B23" s="103" t="n"/>
-      <c r="C23" s="103" t="n"/>
-      <c r="D23" s="103" t="n"/>
-      <c r="E23" s="103" t="n"/>
-      <c r="F23" s="103" t="n"/>
-      <c r="G23" s="103" t="n"/>
-      <c r="H23" s="103" t="n"/>
-      <c r="I23" s="103" t="n"/>
-      <c r="J23" s="103" t="n"/>
-      <c r="K23" s="103" t="n"/>
-      <c r="L23" s="103" t="n"/>
-      <c r="M23" s="103" t="n"/>
-      <c r="N23" s="103" t="n"/>
-      <c r="O23" s="103" t="n"/>
-      <c r="P23" s="104" t="n"/>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="53" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="B24" s="53" t="inlineStr">
-        <is>
-          <t>P6-S10</t>
-        </is>
-      </c>
-      <c r="C24" s="54" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-node</t>
-        </is>
-      </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="E24" s="54" t="inlineStr">
-        <is>
-          <t>market_intel_node — 10th LangGraph node</t>
-        </is>
-      </c>
-      <c r="F24" s="54" t="inlineStr">
-        <is>
-          <t>New parallel domain node. Runs CompetitorEnricher + OccupancyEnricher. Outputs market_intel_output: competitor_pricing, area_occupancy, pricing_alerts. Writes market_assumptions dict. Participates in assumption diffing. Critic receives market context. Supersedes original P6-06.</t>
-        </is>
-      </c>
-      <c r="G24" s="54" t="inlineStr">
-        <is>
-          <t>feat: market_intel_node — 10th parallel LangGraph node, Swiggy-powered market awareness</t>
-        </is>
-      </c>
-      <c r="H24" s="54" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md (market_intel_node section), docs/ARCHITECTURE.md (11-node pipeline), docs/DECISIONS.md (D-020)</t>
-        </is>
-      </c>
-      <c r="I24" s="45" t="inlineStr">
+      <c r="O57" s="70" t="inlineStr">
+        <is>
+          <t>P6-D03</t>
+        </is>
+      </c>
+      <c r="P57" s="70" t="inlineStr">
+        <is>
+          <t>CI passes on clean repo; fails on intentional test break; eval regression detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="52" customHeight="1">
+      <c r="A58" s="48" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="B58" s="48" t="inlineStr">
+        <is>
+          <t>P7-02</t>
+        </is>
+      </c>
+      <c r="C58" s="49" t="inlineStr">
+        <is>
+          <t>feature/phase7-cloud-deploy</t>
+        </is>
+      </c>
+      <c r="D58" s="49" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="E58" s="49" t="inlineStr">
+        <is>
+          <t>Cloud deployment — Railway / Fly.io</t>
+        </is>
+      </c>
+      <c r="F58" s="49" t="inlineStr">
+        <is>
+          <t>Containerise API + frontend. Deploy to Railway or Fly.io. Managed Postgres + Redis + Qdrant. Production env vars. Swiggy OAuth redirect URI updated for production domain. Health endpoint green on production URL.</t>
+        </is>
+      </c>
+      <c r="G58" s="49" t="inlineStr">
+        <is>
+          <t>feat: cloud deployment — production on Railway/Fly.io</t>
+        </is>
+      </c>
+      <c r="H58" s="49" t="inlineStr">
+        <is>
+          <t>docs/ROADMAP.md</t>
+        </is>
+      </c>
+      <c r="I58" s="45" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J24" s="51" t="inlineStr">
+      <c r="J58" s="51" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K24" s="53" t="inlineStr">
+      <c r="K58" s="48" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L24" s="53" t="inlineStr"/>
-      <c r="M24" s="53" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="N24" s="55" t="n">
+      <c r="L58" s="48" t="inlineStr"/>
+      <c r="M58" s="48" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="N58" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="54" t="inlineStr">
-        <is>
-          <t>P6-S09</t>
-        </is>
-      </c>
-      <c r="P24" s="54" t="inlineStr">
-        <is>
-          <t>Node writes market_intel_output + market_assumptions; parallel verified; assumption diffing fires; LangSmith trace shows node</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="48" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="B25" s="48" t="inlineStr">
-        <is>
-          <t>P6-S11</t>
-        </is>
-      </c>
-      <c r="C25" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-dineout-manager-node</t>
-        </is>
-      </c>
-      <c r="D25" s="49" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="E25" s="49" t="inlineStr">
-        <is>
-          <t>dineout_manager_node — 11th LangGraph node</t>
-        </is>
-      </c>
-      <c r="F25" s="49" t="inlineStr">
-        <is>
-          <t>New parallel domain node. get_booking_status checks your own Dineout booking density. get_available_slots checks remaining capacity. If reservation node predicts high walk-in AND slots low → queues book_table action. Writes dineout_assumptions dict.</t>
-        </is>
-      </c>
-      <c r="G25" s="49" t="inlineStr">
-        <is>
-          <t>feat: dineout_manager_node — 11th parallel LangGraph node, manages your Dineout presence</t>
-        </is>
-      </c>
-      <c r="H25" s="49" t="inlineStr">
-        <is>
-          <t>docs/AGENTS.md (dineout_manager_node section), docs/ARCHITECTURE.md</t>
-        </is>
-      </c>
-      <c r="I25" s="45" t="inlineStr">
+      <c r="O58" s="49" t="inlineStr">
+        <is>
+          <t>P7-01</t>
+        </is>
+      </c>
+      <c r="P58" s="49" t="inlineStr">
+        <is>
+          <t>Production URL health check green; all env vars; Swiggy OAuth works on production domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="52" customHeight="1">
+      <c r="A59" s="69" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="B59" s="69" t="inlineStr">
+        <is>
+          <t>P7-03</t>
+        </is>
+      </c>
+      <c r="C59" s="70" t="inlineStr">
+        <is>
+          <t>feature/phase7-prod-hardening</t>
+        </is>
+      </c>
+      <c r="D59" s="70" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="E59" s="70" t="inlineStr">
+        <is>
+          <t>Production hardening</t>
+        </is>
+      </c>
+      <c r="F59" s="70" t="inlineStr">
+        <is>
+          <t>Rate limiting (slowapi). Secrets management (not env file). CORS lockdown. JWT key rotation. Sentry alerts tuned for production. Load test with k6.</t>
+        </is>
+      </c>
+      <c r="G59" s="70" t="inlineStr">
+        <is>
+          <t>feat: production hardening — rate limiting, secrets, CORS, JWT rotation</t>
+        </is>
+      </c>
+      <c r="H59" s="70" t="inlineStr">
+        <is>
+          <t>docs/ROADMAP.md</t>
+        </is>
+      </c>
+      <c r="I59" s="45" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J25" s="51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K25" s="48" t="inlineStr">
+      <c r="J59" s="56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K59" s="69" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L25" s="48" t="inlineStr"/>
-      <c r="M25" s="48" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="N25" s="50" t="n">
+      <c r="L59" s="69" t="inlineStr"/>
+      <c r="M59" s="69" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="N59" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="49" t="inlineStr">
-        <is>
-          <t>P6-S10</t>
-        </is>
-      </c>
-      <c r="P25" s="49" t="inlineStr">
-        <is>
-          <t>Writes dineout_manager_output + dineout_assumptions; book_table action queued when conditions met; LangSmith trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="52" customHeight="1">
-      <c r="A26" s="53" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="B26" s="53" t="inlineStr">
-        <is>
-          <t>P6-S12</t>
-        </is>
-      </c>
-      <c r="C26" s="54" t="inlineStr">
-        <is>
-          <t>feature/swiggy-market-intel-node</t>
-        </is>
-      </c>
-      <c r="D26" s="54" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="E26" s="54" t="inlineStr">
-        <is>
-          <t>Assumption diffs 5 + 6 for new nodes</t>
-        </is>
-      </c>
-      <c r="F26" s="54" t="inlineStr">
-        <is>
-          <t>Diff 5: market_intel assumed_competitor_avg_price vs menu_intel items_assumed_available pricing. Diff 6: dineout_manager assumed_dineout_slots_low vs reservation assumed_peak_occupancy. Extends P6-00b. Total now 5 active diffs.</t>
-        </is>
-      </c>
-      <c r="G26" s="54" t="inlineStr">
-        <is>
-          <t>feat: assumption diffs 5+6 — market vs menu pricing, dineout slots vs reservation occupancy</t>
-        </is>
-      </c>
-      <c r="H26" s="54" t="inlineStr">
-        <is>
-          <t>docs/ARCHITECTURE.md (sanity checker updated), docs/AGENTS.md</t>
-        </is>
-      </c>
-      <c r="I26" s="45" t="inlineStr">
+      <c r="O59" s="70" t="inlineStr">
+        <is>
+          <t>P7-02</t>
+        </is>
+      </c>
+      <c r="P59" s="70" t="inlineStr">
+        <is>
+          <t>Rate limit smoke test; CORS rejection; Sentry alert fires on 500; k6 load test passes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="52" customHeight="1">
+      <c r="A60" s="48" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="B60" s="48" t="inlineStr">
+        <is>
+          <t>P7-04</t>
+        </is>
+      </c>
+      <c r="C60" s="49" t="inlineStr">
+        <is>
+          <t>feature/phase7-docs-website</t>
+        </is>
+      </c>
+      <c r="D60" s="49" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="E60" s="49" t="inlineStr">
+        <is>
+          <t>Mintlify docs website</t>
+        </is>
+      </c>
+      <c r="F60" s="49" t="inlineStr">
+        <is>
+          <t>Point Mintlify at docs/ folder. Navigation: architecture, connectors, agents, API reference, Swiggy integration guide, evaluation, deployment. Custom domain. Public URL to share with Swiggy team, recruiters, restaurant clients.</t>
+        </is>
+      </c>
+      <c r="G60" s="49" t="inlineStr">
+        <is>
+          <t>feat: Mintlify docs website — public-facing CortexKitchen v2 documentation</t>
+        </is>
+      </c>
+      <c r="H60" s="49" t="inlineStr">
+        <is>
+          <t>All docs/ files</t>
+        </is>
+      </c>
+      <c r="I60" s="45" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J26" s="56" t="inlineStr">
+      <c r="J60" s="56" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K26" s="53" t="inlineStr">
+      <c r="K60" s="48" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L26" s="53" t="inlineStr"/>
-      <c r="M26" s="53" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="N26" s="55" t="n">
+      <c r="L60" s="48" t="inlineStr"/>
+      <c r="M60" s="48" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="N60" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="54" t="inlineStr">
-        <is>
-          <t>P6-S10</t>
-        </is>
-      </c>
-      <c r="P26" s="54" t="inlineStr">
-        <is>
-          <t>Diff 5 + 6 fire correctly; existing 3 diffs unaffected; stale_assumptions includes new conflicts</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="57" t="inlineStr">
-        <is>
-          <t>WEEK 5 — Action Layer: Execution + Approval Gates</t>
-        </is>
-      </c>
-      <c r="B28" s="103" t="n"/>
-      <c r="C28" s="103" t="n"/>
-      <c r="D28" s="103" t="n"/>
-      <c r="E28" s="103" t="n"/>
-      <c r="F28" s="103" t="n"/>
-      <c r="G28" s="103" t="n"/>
-      <c r="H28" s="103" t="n"/>
-      <c r="I28" s="103" t="n"/>
-      <c r="J28" s="103" t="n"/>
-      <c r="K28" s="103" t="n"/>
-      <c r="L28" s="103" t="n"/>
-      <c r="M28" s="103" t="n"/>
-      <c r="N28" s="103" t="n"/>
-      <c r="O28" s="103" t="n"/>
-      <c r="P28" s="104" t="n"/>
-    </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="58" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B29" s="58" t="inlineStr">
-        <is>
-          <t>P6-S13</t>
-        </is>
-      </c>
-      <c r="C29" s="59" t="inlineStr">
-        <is>
-          <t>feature/swiggy-action-queue</t>
-        </is>
-      </c>
-      <c r="D29" s="59" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E29" s="59" t="inlineStr">
-        <is>
-          <t>ActionQueueService + action_queue table</t>
-        </is>
-      </c>
-      <c r="F29" s="59" t="inlineStr">
-        <is>
-          <t>New table: id, org_id, action_type (AUTO/APPROVE_REQUIRED/RECOMMENDATION), payload jsonb, status (PENDING/APPROVED/EXECUTED/REJECTED/EXPIRED), approved_by, executed_at, error. ActionQueueService CRUD. Plan output includes action_queue section in API response.</t>
-        </is>
-      </c>
-      <c r="G29" s="59" t="inlineStr">
-        <is>
-          <t>feat: ActionQueueService + action_queue table — 3-tier action model with approval lifecycle</t>
-        </is>
-      </c>
-      <c r="H29" s="59" t="inlineStr">
-        <is>
-          <t>docs/ACTION_QUEUE.md (new), docs/APIS.md (action queue endpoints), docs/DECISIONS.md (D-021)</t>
-        </is>
-      </c>
-      <c r="I29" s="45" t="inlineStr">
+      <c r="O60" s="49" t="inlineStr">
+        <is>
+          <t>P7-03</t>
+        </is>
+      </c>
+      <c r="P60" s="49" t="inlineStr">
+        <is>
+          <t>Docs site live at public URL; all 13 doc files render; search works; no broken links</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="6" customHeight="1">
+      <c r="A61" s="69" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="B61" s="69" t="inlineStr">
+        <is>
+          <t>P7-05</t>
+        </is>
+      </c>
+      <c r="C61" s="70" t="inlineStr">
+        <is>
+          <t>dev -&gt; main PR</t>
+        </is>
+      </c>
+      <c r="D61" s="70" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="E61" s="70" t="inlineStr">
+        <is>
+          <t>Sync Phase 7 to main — public release</t>
+        </is>
+      </c>
+      <c r="F61" s="70" t="inlineStr">
+        <is>
+          <t>Live production URL. README updated with live demo link + docs website link. Apply to jobs immediately. Update portfolio.</t>
+        </is>
+      </c>
+      <c r="G61" s="70" t="inlineStr">
+        <is>
+          <t>release: Phase 7 complete — CortexKitchen v2 live in production</t>
+        </is>
+      </c>
+      <c r="H61" s="70" t="inlineStr">
+        <is>
+          <t>README.md, anoushkavyas.vercel.app portfolio</t>
+        </is>
+      </c>
+      <c r="I61" s="45" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J29" s="51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K29" s="58" t="inlineStr">
+      <c r="J61" s="45" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K61" s="69" t="inlineStr">
         <is>
           <t>Anoushka</t>
         </is>
       </c>
-      <c r="L29" s="58" t="inlineStr"/>
-      <c r="M29" s="58" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="N29" s="60" t="n">
+      <c r="L61" s="69" t="inlineStr"/>
+      <c r="M61" s="69" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="N61" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="59" t="inlineStr">
-        <is>
-          <t>P6-S09</t>
-        </is>
-      </c>
-      <c r="P29" s="59" t="inlineStr">
-        <is>
-          <t>Action CRUD tests; status transitions PENDING→APPROVED→EXECUTED; plan response includes action_queue; expired cleanup</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="48" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B30" s="48" t="inlineStr">
-        <is>
-          <t>P6-S14</t>
-        </is>
-      </c>
-      <c r="C30" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-procurement-l2</t>
-        </is>
-      </c>
-      <c r="D30" s="49" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="E30" s="49" t="inlineStr">
-        <is>
-          <t>ProcurementExecutor — Instamart checkout (ReAct pattern)</t>
-        </is>
-      </c>
-      <c r="F30" s="49" t="inlineStr">
-        <is>
-          <t>ReAct-style execution (absorbs original P6-05): LLM observes search_products result, refines query if needed (max 3 iterations), selects variant. Then: get_cart → clear_cart → update_cart (spinIds) → get_cart → LangGraph interrupt() → owner approval → checkout. Check-then-retry on 5xx. procurement_orders table.</t>
-        </is>
-      </c>
-      <c r="G30" s="49" t="inlineStr">
-        <is>
-          <t>feat: ProcurementExecutor — ReAct ingredient search + Instamart checkout with approval gate</t>
-        </is>
-      </c>
-      <c r="H30" s="49" t="inlineStr">
-        <is>
-          <t>docs/ACTION_QUEUE.md (procurement flow), docs/SWIGGY_INTEGRATION.md (checkout non-idempotency)</t>
-        </is>
-      </c>
-      <c r="I30" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J30" s="51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K30" s="48" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L30" s="48" t="inlineStr"/>
-      <c r="M30" s="48" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="N30" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="49" t="inlineStr">
-        <is>
-          <t>P6-S13</t>
-        </is>
-      </c>
-      <c r="P30" s="49" t="inlineStr">
-        <is>
-          <t>ReAct max 3 iterations; check-then-retry on 5xx; interrupt() pauses graph; approval resumes checkout; procurement_orders row created</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="58" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B31" s="58" t="inlineStr">
-        <is>
-          <t>P6-S15</t>
-        </is>
-      </c>
-      <c r="C31" s="59" t="inlineStr">
-        <is>
-          <t>feature/swiggy-action-queue</t>
-        </is>
-      </c>
-      <c r="D31" s="59" t="inlineStr">
-        <is>
-          <t>Agents</t>
-        </is>
-      </c>
-      <c r="E31" s="59" t="inlineStr">
-        <is>
-          <t>Dineout table booking execution</t>
-        </is>
-      </c>
-      <c r="F31" s="59" t="inlineStr">
-        <is>
-          <t>When dineout_manager_node queues book_table and owner approves: create_cart (DEAL_TICKET_PURCHASE) → book_table (slotId, itemId, reservationTime, guestCount, lat/lng). On 5xx: get_booking_status before retry. Confirmation written to reservations table.</t>
-        </is>
-      </c>
-      <c r="G31" s="59" t="inlineStr">
-        <is>
-          <t>feat: Dineout table booking execution with approval gate</t>
-        </is>
-      </c>
-      <c r="H31" s="59" t="inlineStr">
-        <is>
-          <t>docs/SWIGGY_INTEGRATION.md (book_table non-idempotency), docs/ACTION_QUEUE.md</t>
-        </is>
-      </c>
-      <c r="I31" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J31" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K31" s="58" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L31" s="58" t="inlineStr"/>
-      <c r="M31" s="58" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="N31" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="59" t="inlineStr">
-        <is>
-          <t>P6-S13</t>
-        </is>
-      </c>
-      <c r="P31" s="59" t="inlineStr">
-        <is>
-          <t>Non-idempotent retry test; end-to-end approval flow; confirmation in reservations table; rejection has no side effects</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="61" t="inlineStr">
-        <is>
-          <t>WEEK 6 — Product Modes: Brief, Live, MCP Expansion</t>
-        </is>
-      </c>
-      <c r="B33" s="103" t="n"/>
-      <c r="C33" s="103" t="n"/>
-      <c r="D33" s="103" t="n"/>
-      <c r="E33" s="103" t="n"/>
-      <c r="F33" s="103" t="n"/>
-      <c r="G33" s="103" t="n"/>
-      <c r="H33" s="103" t="n"/>
-      <c r="I33" s="103" t="n"/>
-      <c r="J33" s="103" t="n"/>
-      <c r="K33" s="103" t="n"/>
-      <c r="L33" s="103" t="n"/>
-      <c r="M33" s="103" t="n"/>
-      <c r="N33" s="103" t="n"/>
-      <c r="O33" s="103" t="n"/>
-      <c r="P33" s="104" t="n"/>
-    </row>
-    <row r="34" ht="52" customHeight="1">
-      <c r="A34" s="62" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B34" s="62" t="inlineStr">
-        <is>
-          <t>P6-S16</t>
-        </is>
-      </c>
-      <c r="C34" s="63" t="inlineStr">
-        <is>
-          <t>feature/swiggy-brief-mode</t>
-        </is>
-      </c>
-      <c r="D34" s="63" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E34" s="63" t="inlineStr">
-        <is>
-          <t>BriefingService — automated 7am daily brief</t>
-        </is>
-      </c>
-      <c r="F34" s="63" t="inlineStr">
-        <is>
-          <t>APScheduler job at 07:00 IST per org. Lightweight run: demand_forecast + market_intel_node only. Pulls overnight Swiggy signals (get_food_orders since last run, track_food_order performance). Generates daily_brief JSON. Stores in daily_briefs table. Email digest (extends P5-11).</t>
-        </is>
-      </c>
-      <c r="G34" s="63" t="inlineStr">
-        <is>
-          <t>feat: BriefingService — automated daily morning brief with overnight Swiggy signals</t>
-        </is>
-      </c>
-      <c r="H34" s="63" t="inlineStr">
-        <is>
-          <t>docs/PRODUCT_MODES.md (new, brief mode), docs/APIS.md (brief endpoints)</t>
-        </is>
-      </c>
-      <c r="I34" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J34" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K34" s="62" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L34" s="62" t="inlineStr"/>
-      <c r="M34" s="62" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="N34" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="63" t="inlineStr">
-        <is>
-          <t>P6-S09</t>
-        </is>
-      </c>
-      <c r="P34" s="63" t="inlineStr">
-        <is>
-          <t>Scheduler fires at correct time; brief generates without full pipeline; daily_briefs row created; email sends</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="52" customHeight="1">
-      <c r="A35" s="48" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B35" s="48" t="inlineStr">
-        <is>
-          <t>P6-S17</t>
-        </is>
-      </c>
-      <c r="C35" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-live-mode</t>
-        </is>
-      </c>
-      <c r="D35" s="49" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E35" s="49" t="inlineStr">
-        <is>
-          <t>LiveMonitorService — real-time during service hours</t>
-        </is>
-      </c>
-      <c r="F35" s="49" t="inlineStr">
-        <is>
-          <t>SSE feed during service hours (12:00-14:00, 19:00-22:00 IST). Polls every 30s: get_food_orders (active), track_food_order (in-flight), track_order (Instamart procurement). Alerts: delivery &gt; threshold, order spike, ingredient arrived. Stops outside service window.</t>
-        </is>
-      </c>
-      <c r="G35" s="49" t="inlineStr">
-        <is>
-          <t>feat: LiveMonitorService — real-time SSE ops monitor during service hours</t>
-        </is>
-      </c>
-      <c r="H35" s="49" t="inlineStr">
-        <is>
-          <t>docs/PRODUCT_MODES.md (live mode section), docs/APIS.md (live SSE endpoint)</t>
-        </is>
-      </c>
-      <c r="I35" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J35" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K35" s="48" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L35" s="48" t="inlineStr"/>
-      <c r="M35" s="48" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="N35" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="49" t="inlineStr">
-        <is>
-          <t>P6-S14</t>
-        </is>
-      </c>
-      <c r="P35" s="49" t="inlineStr">
-        <is>
-          <t>SSE events fire; 30s poll verified; alerts trigger correctly; stops outside service hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="52" customHeight="1">
-      <c r="A36" s="62" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B36" s="62" t="inlineStr">
-        <is>
-          <t>P6-S18</t>
-        </is>
-      </c>
-      <c r="C36" s="63" t="inlineStr">
-        <is>
-          <t>feature/swiggy-mcp-tools</t>
-        </is>
-      </c>
-      <c r="D36" s="63" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="E36" s="63" t="inlineStr">
-        <is>
-          <t>3 new CortexKitchen MCP server tools</t>
-        </is>
-      </c>
-      <c r="F36" s="63" t="inlineStr">
-        <is>
-          <t>Add to mcp_server.py: get_market_brief (calls MarketIntelService live, returns competitor snapshot for Claude Desktop), get_action_queue (pending actions awaiting approval), approve_action (owner approves from Claude Desktop, triggers execution). JWT auth on all 3.</t>
-        </is>
-      </c>
-      <c r="G36" s="63" t="inlineStr">
-        <is>
-          <t>feat: 3 new MCP tools — get_market_brief, get_action_queue, approve_action</t>
-        </is>
-      </c>
-      <c r="H36" s="63" t="inlineStr">
-        <is>
-          <t>docs/APIS.md (MCP tools section), docs/ARCHITECTURE.md (MCP server updated)</t>
-        </is>
-      </c>
-      <c r="I36" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J36" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K36" s="62" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L36" s="62" t="inlineStr"/>
-      <c r="M36" s="62" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="N36" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="63" t="inlineStr">
-        <is>
-          <t>P6-S13</t>
-        </is>
-      </c>
-      <c r="P36" s="63" t="inlineStr">
-        <is>
-          <t>All 3 tools smoke-tested in Claude Desktop; approve_action triggers execution end-to-end; JWT enforced</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="33" t="inlineStr">
-        <is>
-          <t>WEEK 6-7 — Original P6 Tasks (POS Connector + Voice)</t>
-        </is>
-      </c>
-      <c r="B38" s="103" t="n"/>
-      <c r="C38" s="103" t="n"/>
-      <c r="D38" s="103" t="n"/>
-      <c r="E38" s="103" t="n"/>
-      <c r="F38" s="103" t="n"/>
-      <c r="G38" s="103" t="n"/>
-      <c r="H38" s="103" t="n"/>
-      <c r="I38" s="103" t="n"/>
-      <c r="J38" s="103" t="n"/>
-      <c r="K38" s="103" t="n"/>
-      <c r="L38" s="103" t="n"/>
-      <c r="M38" s="103" t="n"/>
-      <c r="N38" s="103" t="n"/>
-      <c r="O38" s="103" t="n"/>
-      <c r="P38" s="104" t="n"/>
-    </row>
-    <row r="39" ht="52" customHeight="1">
-      <c r="A39" s="65" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B39" s="65" t="inlineStr">
-        <is>
-          <t>P6-R01</t>
-        </is>
-      </c>
-      <c r="C39" s="66" t="inlineStr">
-        <is>
-          <t>feature/swiggy-pos-connector</t>
-        </is>
-      </c>
-      <c r="D39" s="66" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="E39" s="66" t="inlineStr">
-        <is>
-          <t>POS connector — Square/Toast CSV (2nd connector)</t>
-        </is>
-      </c>
-      <c r="F39" s="66" t="inlineStr">
-        <is>
-          <t>Second implementation of BaseConnector. CSV import from Square/Toast export. Maps dine-in orders to orders table with source='pos', channel='dine_in'. Dedup by external_order_id. Validates against InventoryService and ForecastService. Now ForecastService has both delivery (Swiggy) and dine-in (POS) channels.</t>
-        </is>
-      </c>
-      <c r="G39" s="66" t="inlineStr">
-        <is>
-          <t>feat: POSConnector — Square/Toast CSV import, source=pos, channel=dine_in</t>
-        </is>
-      </c>
-      <c r="H39" s="66" t="inlineStr">
-        <is>
-          <t>docs/CONNECTORS.md (POSConnector section), docs/DATA_SOURCES.md (POS section)</t>
-        </is>
-      </c>
-      <c r="I39" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J39" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K39" s="65" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L39" s="65" t="inlineStr"/>
-      <c r="M39" s="65" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="N39" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="66" t="inlineStr">
-        <is>
-          <t>P6-S03</t>
-        </is>
-      </c>
-      <c r="P39" s="66" t="inlineStr">
-        <is>
-          <t>CSV import unit tests; ForecastService integration with both channels; dedup test; InventoryService validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="52" customHeight="1">
-      <c r="A40" s="48" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B40" s="48" t="inlineStr">
-        <is>
-          <t>P6-R02</t>
-        </is>
-      </c>
-      <c r="C40" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-voice-interface</t>
-        </is>
-      </c>
-      <c r="D40" s="49" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="E40" s="49" t="inlineStr">
-        <is>
-          <t>Voice interface — Whisper + RAG chatbot</t>
-        </is>
-      </c>
-      <c r="F40" s="49" t="inlineStr">
-        <is>
-          <t>Whisper transcription on browser-recorded question (MediaRecorder API). RAG chatbot (P5-12) answers. TTS reads back. Manager asks questions while walking the floor. Works with both synthetic and real Swiggy data now in DB. Blocked on P5-12 (already done).</t>
-        </is>
-      </c>
-      <c r="G40" s="49" t="inlineStr">
-        <is>
-          <t>feat: voice interface — Whisper transcription + RAG answer + TTS readback</t>
-        </is>
-      </c>
-      <c r="H40" s="49" t="inlineStr">
-        <is>
-          <t>docs/PRODUCT_MODES.md (voice section)</t>
-        </is>
-      </c>
-      <c r="I40" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J40" s="45" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K40" s="48" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L40" s="48" t="inlineStr"/>
-      <c r="M40" s="48" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="N40" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="49" t="inlineStr">
-        <is>
-          <t>P6-S16</t>
-        </is>
-      </c>
-      <c r="P40" s="49" t="inlineStr">
-        <is>
-          <t>Transcription accuracy smoke test; end-to-end voice → RAG answer → TTS; works with real Swiggy data in DB</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="6" customHeight="1"/>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="42" t="inlineStr">
-        <is>
-          <t>WEEK 7 — Frontend: 5 New Pages + 3 New Panels</t>
-        </is>
-      </c>
-      <c r="B42" s="103" t="n"/>
-      <c r="C42" s="103" t="n"/>
-      <c r="D42" s="103" t="n"/>
-      <c r="E42" s="103" t="n"/>
-      <c r="F42" s="103" t="n"/>
-      <c r="G42" s="103" t="n"/>
-      <c r="H42" s="103" t="n"/>
-      <c r="I42" s="103" t="n"/>
-      <c r="J42" s="103" t="n"/>
-      <c r="K42" s="103" t="n"/>
-      <c r="L42" s="103" t="n"/>
-      <c r="M42" s="103" t="n"/>
-      <c r="N42" s="103" t="n"/>
-      <c r="O42" s="103" t="n"/>
-      <c r="P42" s="104" t="n"/>
-    </row>
-    <row r="43" ht="52" customHeight="1">
-      <c r="A43" s="43" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B43" s="43" t="inlineStr">
-        <is>
-          <t>P6-F01</t>
-        </is>
-      </c>
-      <c r="C43" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-frontend-market</t>
-        </is>
-      </c>
-      <c r="D43" s="44" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="E43" s="44" t="inlineStr">
-        <is>
-          <t>Market intelligence panel (planning results page)</t>
-        </is>
-      </c>
-      <c r="F43" s="44" t="inlineStr">
-        <is>
-          <t>New panel on /runs/{id}. Competitor pricing table: your price vs area avg vs cheapest competitor per dish category. Area occupancy badge (HIGH/MEDIUM/LOW). Instamart prices for shortage items. Pricing alerts (red if &gt;20% above area avg). Hidden when market_intel_output absent.</t>
-        </is>
-      </c>
-      <c r="G43" s="44" t="inlineStr">
-        <is>
-          <t>feat: market intelligence panel — competitor pricing + area occupancy on planning results</t>
-        </is>
-      </c>
-      <c r="H43" s="44" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="I43" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J43" s="51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K43" s="43" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L43" s="43" t="inlineStr"/>
-      <c r="M43" s="43" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="N43" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="44" t="inlineStr">
-        <is>
-          <t>P6-S10</t>
-        </is>
-      </c>
-      <c r="P43" s="44" t="inlineStr">
-        <is>
-          <t>Panel renders when data present; hides gracefully when not; pricing alerts correct; occupancy badge correct</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="52" customHeight="1">
-      <c r="A44" s="48" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B44" s="48" t="inlineStr">
-        <is>
-          <t>P6-F02</t>
-        </is>
-      </c>
-      <c r="C44" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-frontend-actions</t>
-        </is>
-      </c>
-      <c r="D44" s="49" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="E44" s="49" t="inlineStr">
-        <is>
-          <t>Action queue UI + procurement tracker</t>
-        </is>
-      </c>
-      <c r="F44" s="49" t="inlineStr">
-        <is>
-          <t>New section below plan output. Lists pending actions with type badge. Approve/Reject buttons for APPROVE_REQUIRED. Instamart cart preview modal (items, total, ETA) before approving checkout. Procurement tracker in inventory panel: placed orders, status, ETA.</t>
-        </is>
-      </c>
-      <c r="G44" s="49" t="inlineStr">
-        <is>
-          <t>feat: action queue UI — approve/reject with cart preview, procurement tracker</t>
-        </is>
-      </c>
-      <c r="H44" s="49" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="I44" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J44" s="51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K44" s="48" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L44" s="48" t="inlineStr"/>
-      <c r="M44" s="48" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="N44" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="49" t="inlineStr">
-        <is>
-          <t>P6-S13</t>
-        </is>
-      </c>
-      <c r="P44" s="49" t="inlineStr">
-        <is>
-          <t>Action list renders; approve triggers API; cart preview correct; reject has no side effects; tracker updates on delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="52" customHeight="1">
-      <c r="A45" s="43" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B45" s="43" t="inlineStr">
-        <is>
-          <t>P6-F03</t>
-        </is>
-      </c>
-      <c r="C45" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-frontend-brief</t>
-        </is>
-      </c>
-      <c r="D45" s="44" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="E45" s="44" t="inlineStr">
-        <is>
-          <t>/brief page — daily morning briefing</t>
-        </is>
-      </c>
-      <c r="F45" s="44" t="inlineStr">
-        <is>
-          <t>New route /brief. Overnight Swiggy performance (orders, avg delivery time, late %), today's demand forecast vs yesterday, top 3 action priorities, market snapshot. Auto-refreshes if brief is stale. Empty state when no brief yet.</t>
-        </is>
-      </c>
-      <c r="G45" s="44" t="inlineStr">
-        <is>
-          <t>feat: /brief page — daily morning operational briefing</t>
-        </is>
-      </c>
-      <c r="H45" s="44" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="I45" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J45" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K45" s="43" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L45" s="43" t="inlineStr"/>
-      <c r="M45" s="43" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="N45" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="44" t="inlineStr">
-        <is>
-          <t>P6-S16</t>
-        </is>
-      </c>
-      <c r="P45" s="44" t="inlineStr">
-        <is>
-          <t>Page loads; stale brief triggers refresh; all 4 sections render; empty state works</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="52" customHeight="1">
-      <c r="A46" s="48" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B46" s="48" t="inlineStr">
-        <is>
-          <t>P6-F04</t>
-        </is>
-      </c>
-      <c r="C46" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-frontend-connectors</t>
-        </is>
-      </c>
-      <c r="D46" s="49" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="E46" s="49" t="inlineStr">
-        <is>
-          <t>/connectors page — data source management</t>
-        </is>
-      </c>
-      <c r="F46" s="49" t="inlineStr">
-        <is>
-          <t>New route /connectors. Lists connectors with status badges (Connected/Disconnected/Error). Shows last sync time, records synced, data freshness. Connect button triggers OAuth flow. Disconnect revokes token. Error state shows last error + reconnect. Works for Swiggy + future POS connector.</t>
-        </is>
-      </c>
-      <c r="G46" s="49" t="inlineStr">
-        <is>
-          <t>feat: /connectors page — platform data source management with OAuth connect flow</t>
-        </is>
-      </c>
-      <c r="H46" s="49" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="I46" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J46" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K46" s="48" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L46" s="48" t="inlineStr"/>
-      <c r="M46" s="48" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="N46" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="49" t="inlineStr">
-        <is>
-          <t>P6-S01</t>
-        </is>
-      </c>
-      <c r="P46" s="49" t="inlineStr">
-        <is>
-          <t>Connect triggers OAuth; post-OAuth shows Connected; Disconnect revokes; error state renders; POS connector appears as available</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="52" customHeight="1">
-      <c r="A47" s="43" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B47" s="43" t="inlineStr">
-        <is>
-          <t>P6-F05</t>
-        </is>
-      </c>
-      <c r="C47" s="44" t="inlineStr">
-        <is>
-          <t>feature/swiggy-frontend-live</t>
-        </is>
-      </c>
-      <c r="D47" s="44" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="E47" s="44" t="inlineStr">
-        <is>
-          <t>/live page — real-time ops monitor</t>
-        </is>
-      </c>
-      <c r="F47" s="44" t="inlineStr">
-        <is>
-          <t>New route /live. Active during service hours (countdown outside). SSE feed: active Swiggy orders + ETA, delivery performance gauge (green/amber/red), Instamart procurement in-flight status, alert feed (last 10). Auto-connects SSE on load.</t>
-        </is>
-      </c>
-      <c r="G47" s="44" t="inlineStr">
-        <is>
-          <t>feat: /live page — real-time service-hours ops monitor via SSE</t>
-        </is>
-      </c>
-      <c r="H47" s="44" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="I47" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J47" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K47" s="43" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L47" s="43" t="inlineStr"/>
-      <c r="M47" s="43" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="N47" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="44" t="inlineStr">
-        <is>
-          <t>P6-S17</t>
-        </is>
-      </c>
-      <c r="P47" s="44" t="inlineStr">
-        <is>
-          <t>SSE connects; events update UI; countdown outside hours; gauge updates; alert feed shows last 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="52" customHeight="1">
-      <c r="A48" s="48" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B48" s="48" t="inlineStr">
-        <is>
-          <t>P6-F06</t>
-        </is>
-      </c>
-      <c r="C48" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-frontend-market</t>
-        </is>
-      </c>
-      <c r="D48" s="49" t="inlineStr">
-        <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="E48" s="49" t="inlineStr">
-        <is>
-          <t>Dashboard enhancements</t>
-        </is>
-      </c>
-      <c r="F48" s="49" t="inlineStr">
-        <is>
-          <t>Add to existing dashboard: connector status widget (data source health bar), brief mode trigger button, today's Swiggy KPIs (orders today, delivery rating, top Swiggy seller), data_sources column on /runs list.</t>
-        </is>
-      </c>
-      <c r="G48" s="49" t="inlineStr">
-        <is>
-          <t>feat: dashboard — connector status widget, brief trigger, live Swiggy KPIs, data_sources on runs list</t>
-        </is>
-      </c>
-      <c r="H48" s="49" t="inlineStr">
-        <is>
-          <t>None (frontend only)</t>
-        </is>
-      </c>
-      <c r="I48" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J48" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K48" s="48" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L48" s="48" t="inlineStr"/>
-      <c r="M48" s="48" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="N48" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="49" t="inlineStr">
-        <is>
-          <t>P6-S16</t>
-        </is>
-      </c>
-      <c r="P48" s="49" t="inlineStr">
-        <is>
-          <t>Connector widget shows status; brief trigger fires; Swiggy KPIs render; runs list data_sources column correct</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="6" customHeight="1"/>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="61" t="inlineStr">
-        <is>
-          <t>WEEK 8 — Docs + Merge: Phase 6 Complete</t>
-        </is>
-      </c>
-      <c r="B50" s="103" t="n"/>
-      <c r="C50" s="103" t="n"/>
-      <c r="D50" s="103" t="n"/>
-      <c r="E50" s="103" t="n"/>
-      <c r="F50" s="103" t="n"/>
-      <c r="G50" s="103" t="n"/>
-      <c r="H50" s="103" t="n"/>
-      <c r="I50" s="103" t="n"/>
-      <c r="J50" s="103" t="n"/>
-      <c r="K50" s="103" t="n"/>
-      <c r="L50" s="103" t="n"/>
-      <c r="M50" s="103" t="n"/>
-      <c r="N50" s="103" t="n"/>
-      <c r="O50" s="103" t="n"/>
-      <c r="P50" s="104" t="n"/>
-    </row>
-    <row r="51" ht="52" customHeight="1">
-      <c r="A51" s="62" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B51" s="62" t="inlineStr">
-        <is>
-          <t>P6-D01</t>
-        </is>
-      </c>
-      <c r="C51" s="63" t="inlineStr">
-        <is>
-          <t>feature/swiggy-docs</t>
-        </is>
-      </c>
-      <c r="D51" s="63" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="E51" s="63" t="inlineStr">
-        <is>
-          <t>5 new documentation files</t>
-        </is>
-      </c>
-      <c r="F51" s="63" t="inlineStr">
-        <is>
-          <t>CONNECTORS.md: BaseConnector interface, sync vs enrich, how to add new connector. SWIGGY_INTEGRATION.md: all 22 tools, parameter mappings, OAuth, rate limits, error handling. ACTION_QUEUE.md: action types, approval flow, non-idempotent patterns. DATA_SOURCES.md: all sources, channels, sync frequency. PRODUCT_MODES.md: ops/brief/live/voice mode specs.</t>
-        </is>
-      </c>
-      <c r="G51" s="63" t="inlineStr">
-        <is>
-          <t>docs: 5 new documentation files for Phase 6 connector + action + product mode layer</t>
-        </is>
-      </c>
-      <c r="H51" s="63" t="inlineStr">
-        <is>
-          <t>docs/CONNECTORS.md, docs/SWIGGY_INTEGRATION.md, docs/ACTION_QUEUE.md, docs/DATA_SOURCES.md, docs/PRODUCT_MODES.md</t>
-        </is>
-      </c>
-      <c r="I51" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J51" s="51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K51" s="62" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L51" s="62" t="inlineStr"/>
-      <c r="M51" s="62" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="N51" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="63" t="inlineStr">
-        <is>
-          <t>P6-F06</t>
-        </is>
-      </c>
-      <c r="P51" s="63" t="inlineStr">
-        <is>
-          <t>All 5 files present; no broken links; tool parameter tables accurate vs Swiggy docs</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="52" customHeight="1">
-      <c r="A52" s="48" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B52" s="48" t="inlineStr">
-        <is>
-          <t>P6-D02</t>
-        </is>
-      </c>
-      <c r="C52" s="49" t="inlineStr">
-        <is>
-          <t>feature/swiggy-docs</t>
-        </is>
-      </c>
-      <c r="D52" s="49" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="E52" s="49" t="inlineStr">
-        <is>
-          <t>Update 8 existing docs</t>
-        </is>
-      </c>
-      <c r="F52" s="49" t="inlineStr">
-        <is>
-          <t>ARCHITECTURE.md: connector layer, 11-node pipeline, action layer, product modes. AGENTS.md: 2 new nodes + 2 new diffs. APIS.md: all new endpoints. DATA_MODEL.md: 6 new tables. DECISIONS.md: D-019 through D-022. ROADMAP.md: Phase 6 in-progress. EVALUATION.md: new node eval criteria. README.md: updated product headline.</t>
-        </is>
-      </c>
-      <c r="G52" s="49" t="inlineStr">
-        <is>
-          <t>docs: update 8 existing docs to reflect full Phase 6 additions</t>
-        </is>
-      </c>
-      <c r="H52" s="49" t="inlineStr">
-        <is>
-          <t>ARCHITECTURE, AGENTS, APIS, DATA_MODEL, DECISIONS, ROADMAP, EVALUATION, README</t>
-        </is>
-      </c>
-      <c r="I52" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J52" s="51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K52" s="48" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L52" s="48" t="inlineStr"/>
-      <c r="M52" s="48" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="N52" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="49" t="inlineStr">
-        <is>
-          <t>P6-D01</t>
-        </is>
-      </c>
-      <c r="P52" s="49" t="inlineStr">
-        <is>
-          <t>No stale 9-node pipeline references; all new endpoints in APIS.md; D-019 through D-022 in DECISIONS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="52" customHeight="1">
-      <c r="A53" s="62" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B53" s="62" t="inlineStr">
-        <is>
-          <t>P6-D03</t>
-        </is>
-      </c>
-      <c r="C53" s="63" t="inlineStr">
-        <is>
-          <t>dev -&gt; main PR</t>
-        </is>
-      </c>
-      <c r="D53" s="63" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="E53" s="63" t="inlineStr">
-        <is>
-          <t>Phase 6 milestone merge to main</t>
-        </is>
-      </c>
-      <c r="F53" s="63" t="inlineStr">
-        <is>
-          <t>Merge feature/ck-v2-platform → dev → main. All 11 nodes verified in LangSmith. All 22 Swiggy tools exercised in staging. POS connector imports CSV end-to-end. Voice interface smoke tested. Action queue end-to-end. All 3 product modes verified. 5 new frontend pages smoke tested. Full test suite green.</t>
-        </is>
-      </c>
-      <c r="G53" s="63" t="inlineStr">
-        <is>
-          <t>release: Phase 6 complete — CortexKitchen v2 Swiggy-native restaurant OS</t>
-        </is>
-      </c>
-      <c r="H53" s="63" t="inlineStr">
-        <is>
-          <t>README.md (portfolio headline), docs/ROADMAP.md (Phase 6 complete)</t>
-        </is>
-      </c>
-      <c r="I53" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J53" s="46" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K53" s="62" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L53" s="62" t="inlineStr"/>
-      <c r="M53" s="62" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="N53" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="63" t="inlineStr">
-        <is>
-          <t>P6-D02</t>
-        </is>
-      </c>
-      <c r="P53" s="63" t="inlineStr">
-        <is>
-          <t>Full test suite green; 11 nodes in LangSmith; staging demo clean; portfolio README updated; docs website prep checklist done</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="6" customHeight="1"/>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="68" t="inlineStr">
-        <is>
-          <t>PHASE 7 — Production, CI/CD, Docs Website</t>
-        </is>
-      </c>
-      <c r="B55" s="103" t="n"/>
-      <c r="C55" s="103" t="n"/>
-      <c r="D55" s="103" t="n"/>
-      <c r="E55" s="103" t="n"/>
-      <c r="F55" s="103" t="n"/>
-      <c r="G55" s="103" t="n"/>
-      <c r="H55" s="103" t="n"/>
-      <c r="I55" s="103" t="n"/>
-      <c r="J55" s="103" t="n"/>
-      <c r="K55" s="103" t="n"/>
-      <c r="L55" s="103" t="n"/>
-      <c r="M55" s="103" t="n"/>
-      <c r="N55" s="103" t="n"/>
-      <c r="O55" s="103" t="n"/>
-      <c r="P55" s="104" t="n"/>
-    </row>
-    <row r="56" ht="52" customHeight="1">
-      <c r="A56" s="69" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="B56" s="69" t="inlineStr">
-        <is>
-          <t>P7-01</t>
-        </is>
-      </c>
-      <c r="C56" s="70" t="inlineStr">
-        <is>
-          <t>feature/phase7-cicd</t>
-        </is>
-      </c>
-      <c r="D56" s="70" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="E56" s="70" t="inlineStr">
-        <is>
-          <t>CI/CD — GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F56" s="70" t="inlineStr">
-        <is>
-          <t>Automated on every PR: unit + integration + RAGAS evals + DeepEval; lint; type check; frontend build; coverage report. Fail on critic score regression. Cache pip dependencies.</t>
-        </is>
-      </c>
-      <c r="G56" s="70" t="inlineStr">
-        <is>
-          <t>feat: CI/CD — automated test + eval pipeline on every PR</t>
-        </is>
-      </c>
-      <c r="H56" s="70" t="inlineStr">
-        <is>
-          <t>docs/ROADMAP.md</t>
-        </is>
-      </c>
-      <c r="I56" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J56" s="51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K56" s="69" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L56" s="69" t="inlineStr"/>
-      <c r="M56" s="69" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="N56" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="70" t="inlineStr">
-        <is>
-          <t>P6-D03</t>
-        </is>
-      </c>
-      <c r="P56" s="70" t="inlineStr">
-        <is>
-          <t>CI passes on clean repo; fails on intentional test break; eval regression detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="52" customHeight="1">
-      <c r="A57" s="48" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="B57" s="48" t="inlineStr">
-        <is>
-          <t>P7-02</t>
-        </is>
-      </c>
-      <c r="C57" s="49" t="inlineStr">
-        <is>
-          <t>feature/phase7-cloud-deploy</t>
-        </is>
-      </c>
-      <c r="D57" s="49" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="E57" s="49" t="inlineStr">
-        <is>
-          <t>Cloud deployment — Railway / Fly.io</t>
-        </is>
-      </c>
-      <c r="F57" s="49" t="inlineStr">
-        <is>
-          <t>Containerise API + frontend. Deploy to Railway or Fly.io. Managed Postgres + Redis + Qdrant. Production env vars. Swiggy OAuth redirect URI updated for production domain. Health endpoint green on production URL.</t>
-        </is>
-      </c>
-      <c r="G57" s="49" t="inlineStr">
-        <is>
-          <t>feat: cloud deployment — production on Railway/Fly.io</t>
-        </is>
-      </c>
-      <c r="H57" s="49" t="inlineStr">
-        <is>
-          <t>docs/ROADMAP.md</t>
-        </is>
-      </c>
-      <c r="I57" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J57" s="51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K57" s="48" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L57" s="48" t="inlineStr"/>
-      <c r="M57" s="48" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="N57" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="49" t="inlineStr">
-        <is>
-          <t>P7-01</t>
-        </is>
-      </c>
-      <c r="P57" s="49" t="inlineStr">
-        <is>
-          <t>Production URL health check green; all env vars; Swiggy OAuth works on production domain</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="52" customHeight="1">
-      <c r="A58" s="69" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="B58" s="69" t="inlineStr">
-        <is>
-          <t>P7-03</t>
-        </is>
-      </c>
-      <c r="C58" s="70" t="inlineStr">
-        <is>
-          <t>feature/phase7-prod-hardening</t>
-        </is>
-      </c>
-      <c r="D58" s="70" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="E58" s="70" t="inlineStr">
-        <is>
-          <t>Production hardening</t>
-        </is>
-      </c>
-      <c r="F58" s="70" t="inlineStr">
-        <is>
-          <t>Rate limiting (slowapi). Secrets management (not env file). CORS lockdown. JWT key rotation. Sentry alerts tuned for production. Load test with k6.</t>
-        </is>
-      </c>
-      <c r="G58" s="70" t="inlineStr">
-        <is>
-          <t>feat: production hardening — rate limiting, secrets, CORS, JWT rotation</t>
-        </is>
-      </c>
-      <c r="H58" s="70" t="inlineStr">
-        <is>
-          <t>docs/ROADMAP.md</t>
-        </is>
-      </c>
-      <c r="I58" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J58" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K58" s="69" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L58" s="69" t="inlineStr"/>
-      <c r="M58" s="69" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="N58" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="70" t="inlineStr">
-        <is>
-          <t>P7-02</t>
-        </is>
-      </c>
-      <c r="P58" s="70" t="inlineStr">
-        <is>
-          <t>Rate limit smoke test; CORS rejection; Sentry alert fires on 500; k6 load test passes</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="52" customHeight="1">
-      <c r="A59" s="48" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="B59" s="48" t="inlineStr">
+      <c r="O61" s="70" t="inlineStr">
         <is>
           <t>P7-04</t>
         </is>
       </c>
-      <c r="C59" s="49" t="inlineStr">
-        <is>
-          <t>feature/phase7-docs-website</t>
-        </is>
-      </c>
-      <c r="D59" s="49" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="E59" s="49" t="inlineStr">
-        <is>
-          <t>Mintlify docs website</t>
-        </is>
-      </c>
-      <c r="F59" s="49" t="inlineStr">
-        <is>
-          <t>Point Mintlify at docs/ folder. Navigation: architecture, connectors, agents, API reference, Swiggy integration guide, evaluation, deployment. Custom domain. Public URL to share with Swiggy team, recruiters, restaurant clients.</t>
-        </is>
-      </c>
-      <c r="G59" s="49" t="inlineStr">
-        <is>
-          <t>feat: Mintlify docs website — public-facing CortexKitchen v2 documentation</t>
-        </is>
-      </c>
-      <c r="H59" s="49" t="inlineStr">
-        <is>
-          <t>All docs/ files</t>
-        </is>
-      </c>
-      <c r="I59" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J59" s="56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K59" s="48" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L59" s="48" t="inlineStr"/>
-      <c r="M59" s="48" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="N59" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="49" t="inlineStr">
-        <is>
-          <t>P7-03</t>
-        </is>
-      </c>
-      <c r="P59" s="49" t="inlineStr">
-        <is>
-          <t>Docs site live at public URL; all 13 doc files render; search works; no broken links</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="52" customHeight="1">
-      <c r="A60" s="69" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="B60" s="69" t="inlineStr">
-        <is>
-          <t>P7-05</t>
-        </is>
-      </c>
-      <c r="C60" s="70" t="inlineStr">
-        <is>
-          <t>dev -&gt; main PR</t>
-        </is>
-      </c>
-      <c r="D60" s="70" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="E60" s="70" t="inlineStr">
-        <is>
-          <t>Sync Phase 7 to main — public release</t>
-        </is>
-      </c>
-      <c r="F60" s="70" t="inlineStr">
-        <is>
-          <t>Live production URL. README updated with live demo link + docs website link. Apply to jobs immediately. Update portfolio.</t>
-        </is>
-      </c>
-      <c r="G60" s="70" t="inlineStr">
-        <is>
-          <t>release: Phase 7 complete — CortexKitchen v2 live in production</t>
-        </is>
-      </c>
-      <c r="H60" s="70" t="inlineStr">
-        <is>
-          <t>README.md, anoushkavyas.vercel.app portfolio</t>
-        </is>
-      </c>
-      <c r="I60" s="45" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="J60" s="45" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K60" s="69" t="inlineStr">
-        <is>
-          <t>Anoushka</t>
-        </is>
-      </c>
-      <c r="L60" s="69" t="inlineStr"/>
-      <c r="M60" s="69" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="N60" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="70" t="inlineStr">
-        <is>
-          <t>P7-04</t>
-        </is>
-      </c>
-      <c r="P60" s="70" t="inlineStr">
+      <c r="P61" s="70" t="inlineStr">
         <is>
           <t>Full E2E on production URL; demo video recorded; portfolio updated</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A28:P28"/>
@@ -16915,7 +17073,7 @@
       </c>
       <c r="D5" s="49" t="inlineStr">
         <is>
-          <t>Current working base — Phase 6 active (P6-S01/S02/S03 complete, P6-S04 next)</t>
+          <t>Current base — P6-S04 (feature/agent-intelligence) IN PROGRESS; P6-S05/S06 blocked on Swiggy token</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>

--- a/CortexKitchen_Progress_Tracker_v4.xlsx
+++ b/CortexKitchen_Progress_Tracker_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Phase Tracker" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Phase 6" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Doc Strategy" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Git Practices" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Tracker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 6" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doc Strategy" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git Practices" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1042,7 +1042,7 @@
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="77" t="inlineStr">
         <is>
-          <t>Last completed: P6-S03 — SwiggyOrderSyncService, get_food_orders → orders table (2026-06-27)</t>
+          <t>Last completed: P6-S04 — Agent Intelligence Bundle + docs overhaul (phase1_sync removed, all docs updated) (2026-06-29)</t>
         </is>
       </c>
       <c r="B4" s="44" t="inlineStr">
@@ -1078,7 +1078,7 @@
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="76" t="inlineStr">
         <is>
-          <t>Stable: dev through P6-S03; P6-S04 (agent-intelligence) IN PROGRESS → next: P6-S05 (Dineout sync, token pending)</t>
+          <t>Stable: dev through P6-S04; all docs updated to reflect 11-node graph; next: P6-S05 (Dineout sync, token pending) or P6-S07 (CompetitorEnricher)</t>
         </is>
       </c>
       <c r="B5" s="49" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B6" s="44" t="inlineStr">
         <is>
-          <t>feature/swiggy-base-connector</t>
+          <t>feature/swiggy-market-intel-enrichers</t>
         </is>
       </c>
       <c r="C6" s="2" t="n"/>
@@ -1507,11 +1507,11 @@
       </c>
       <c r="B16" s="66" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="C16" s="79" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D16" s="49" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
       </c>
       <c r="H75" s="84" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I75" s="51" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M75" s="87" t="inlineStr"/>
       <c r="N75" s="87" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O75" s="88" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="I14" s="45" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J14" s="51" t="inlineStr">
@@ -13940,7 +13940,7 @@
         </is>
       </c>
       <c r="N14" s="43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="44" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
       </c>
       <c r="I53" s="45" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J53" s="51" t="inlineStr">
@@ -16001,7 +16001,7 @@
         </is>
       </c>
       <c r="N53" s="50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" s="49" t="inlineStr">
         <is>
